--- a/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/xd12r_signed_register.xlsx
+++ b/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/xd12r_signed_register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12R_GT1009A0R0\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A97FF7-0202-40B7-A7EC-0CE27055E3EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407CD3E0-EB75-4FDE-9A27-01EC8DDC4CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BCB3DBB9-7E6D-4331-9ADF-22DDBFE801A5}"/>
   </bookViews>

--- a/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/xd12r_signed_register.xlsx
+++ b/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/xd12r_signed_register.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12R_GT1009A0R0\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407CD3E0-EB75-4FDE-9A27-01EC8DDC4CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020C909D-880F-497A-9B6F-02B569F8F46F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BCB3DBB9-7E6D-4331-9ADF-22DDBFE801A5}"/>
+    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{BCB3DBB9-7E6D-4331-9ADF-22DDBFE801A5}"/>
   </bookViews>
   <sheets>
     <sheet name="dac_a_ofs, dac_b_ofs" sheetId="1" r:id="rId1"/>
-    <sheet name="ldo_ctl" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="ldo_ctl" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="20">
   <si>
     <t>[2]</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -100,6 +101,17 @@
   <si>
     <t>Substitute</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> DAC_A_OFS </t>
+  </si>
+  <si>
+    <t>idx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -654,7 +666,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -760,15 +772,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -779,15 +782,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -806,15 +800,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -842,6 +827,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1166,7 +1169,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="ko-KR"/>
+              <a:endParaRPr lang="ko-KR" altLang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1380,6 +1383,1074 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
+              <c:f>Sheet1!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>v</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$129</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="128"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>121</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>122</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>123</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>124</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>126</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>127</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$2:$D$129</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="128"/>
+                <c:pt idx="0">
+                  <c:v>0.113</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.113</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.113</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.113</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.114</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.114</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.114</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.114</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.115</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.115</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.11600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.11700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.11700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.11700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.11700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.11799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.11799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.11799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.11799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.11899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.121</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.122</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.122</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.122</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.122</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.122</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.123</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.123</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.123</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.124</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.124</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.126</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.126</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.127</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.127</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.127</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.127</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.128</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.128</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.129</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.129</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.13</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.13</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.13100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.13100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.13100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.13100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.13200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.13200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.13300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.13200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.13300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.13300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.13400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.13400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.13500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.13500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.13500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.13500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.113</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.112</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.112</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.11</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.111</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.11</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.11</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.11</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.11</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.109</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.109</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.108</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.108</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.107</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.107</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.106</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.106</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.106</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.106</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.106</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.106</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.105</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.105</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.104</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.104</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.10299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.10299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.10199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.10199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.10199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.10199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.10199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.10199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.10100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.10100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>9.9000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>9.9000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>9.8000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>9.8000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>9.8000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>9.8000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>9.7000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>9.7000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>9.6000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>9.6000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>9.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>9.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>9.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>9.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>9.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>9.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>9.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>9.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>9.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>9.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>9.0999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>9.0999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>9.0999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>9.0999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>8.8999999999999996E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-52E8-4721-9DCA-F7B85C3F29D7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1583860367"/>
+        <c:axId val="1583857487"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1583860367"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1583857487"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1583857487"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1583860367"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
               <c:f>ldo_ctl!$G$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
@@ -1618,7 +2689,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="ko-KR"/>
+              <a:endParaRPr lang="ko-KR" altLang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1818,6 +2889,46 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2889,6 +4000,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -3018,6 +4645,47 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="차트 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F696BB0-87E9-9A6B-D370-89AC59AFE8C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3472,7 +5140,7 @@
     <col min="5" max="7" width="3.75" style="1" customWidth="1"/>
     <col min="8" max="9" width="3.75" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.58203125" style="44" customWidth="1"/>
+    <col min="11" max="11" width="2.58203125" style="1" customWidth="1"/>
     <col min="12" max="12" width="8.08203125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.08203125" style="1" customWidth="1"/>
     <col min="14" max="14" width="14.25" style="1" bestFit="1" customWidth="1"/>
@@ -3488,28 +5156,28 @@
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
-      <c r="K1" s="42"/>
+      <c r="K1" s="6"/>
     </row>
     <row r="2" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="43"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="5"/>
       <c r="M2" s="2"/>
     </row>
     <row r="3" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="39" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="31" t="s">
@@ -3527,13 +5195,13 @@
       <c r="H3" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="60" t="s">
+      <c r="I3" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="61" t="s">
+      <c r="J3" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="42"/>
+      <c r="K3" s="6"/>
       <c r="L3" s="14" t="s">
         <v>16</v>
       </c>
@@ -3542,11 +5210,11 @@
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B4" s="50">
+      <c r="B4" s="44">
         <f>BIN2DEC(_xlfn.CONCAT(C4:I4))</f>
         <v>0</v>
       </c>
-      <c r="C4" s="39">
+      <c r="C4" s="36">
         <v>0</v>
       </c>
       <c r="D4" s="28">
@@ -3564,13 +5232,13 @@
       <c r="H4" s="28">
         <v>0</v>
       </c>
-      <c r="I4" s="54">
-        <v>0</v>
-      </c>
-      <c r="J4" s="59">
+      <c r="I4" s="45">
+        <v>0</v>
+      </c>
+      <c r="J4" s="50">
         <v>64</v>
       </c>
-      <c r="K4" s="42"/>
+      <c r="K4" s="6"/>
       <c r="L4" s="24">
         <v>0</v>
       </c>
@@ -3580,11 +5248,11 @@
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B5" s="48">
+      <c r="B5" s="42">
         <f t="shared" ref="B5:B7" si="0">BIN2DEC(_xlfn.CONCAT(C5:I5))</f>
         <v>1</v>
       </c>
-      <c r="C5" s="40">
+      <c r="C5" s="37">
         <v>0</v>
       </c>
       <c r="D5" s="7">
@@ -3602,13 +5270,13 @@
       <c r="H5" s="7">
         <v>0</v>
       </c>
-      <c r="I5" s="55">
-        <v>1</v>
-      </c>
-      <c r="J5" s="57">
+      <c r="I5" s="46">
+        <v>1</v>
+      </c>
+      <c r="J5" s="48">
         <v>65</v>
       </c>
-      <c r="K5" s="42"/>
+      <c r="K5" s="6"/>
       <c r="L5" s="16">
         <v>1</v>
       </c>
@@ -3618,11 +5286,11 @@
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B6" s="48">
+      <c r="B6" s="42">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="37">
         <v>0</v>
       </c>
       <c r="D6" s="7">
@@ -3640,13 +5308,13 @@
       <c r="H6" s="7">
         <v>1</v>
       </c>
-      <c r="I6" s="55">
-        <v>0</v>
-      </c>
-      <c r="J6" s="57">
+      <c r="I6" s="46">
+        <v>0</v>
+      </c>
+      <c r="J6" s="48">
         <v>66</v>
       </c>
-      <c r="K6" s="42"/>
+      <c r="K6" s="6"/>
       <c r="L6" s="16">
         <v>2</v>
       </c>
@@ -3656,11 +5324,11 @@
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B7" s="48">
+      <c r="B7" s="42">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="37">
         <v>0</v>
       </c>
       <c r="D7" s="7">
@@ -3678,13 +5346,13 @@
       <c r="H7" s="7">
         <v>1</v>
       </c>
-      <c r="I7" s="55">
-        <v>1</v>
-      </c>
-      <c r="J7" s="57">
+      <c r="I7" s="46">
+        <v>1</v>
+      </c>
+      <c r="J7" s="48">
         <v>67</v>
       </c>
-      <c r="K7" s="42"/>
+      <c r="K7" s="6"/>
       <c r="L7" s="16">
         <v>3</v>
       </c>
@@ -3694,11 +5362,11 @@
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B8" s="48">
+      <c r="B8" s="42">
         <f>BIN2DEC(_xlfn.CONCAT(C8:I8))</f>
         <v>4</v>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="37">
         <v>0</v>
       </c>
       <c r="D8" s="7">
@@ -3716,13 +5384,13 @@
       <c r="H8" s="7">
         <v>0</v>
       </c>
-      <c r="I8" s="55">
-        <v>0</v>
-      </c>
-      <c r="J8" s="57">
+      <c r="I8" s="46">
+        <v>0</v>
+      </c>
+      <c r="J8" s="48">
         <v>68</v>
       </c>
-      <c r="K8" s="42"/>
+      <c r="K8" s="6"/>
       <c r="L8" s="16">
         <v>4</v>
       </c>
@@ -3732,11 +5400,11 @@
       </c>
     </row>
     <row r="9" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="48">
+      <c r="B9" s="42">
         <f t="shared" ref="B9:B72" si="2">BIN2DEC(_xlfn.CONCAT(C9:I9))</f>
         <v>5</v>
       </c>
-      <c r="C9" s="40">
+      <c r="C9" s="37">
         <v>0</v>
       </c>
       <c r="D9" s="7">
@@ -3754,15 +5422,15 @@
       <c r="H9" s="7">
         <v>0</v>
       </c>
-      <c r="I9" s="55">
-        <v>1</v>
-      </c>
-      <c r="J9" s="57">
+      <c r="I9" s="46">
+        <v>1</v>
+      </c>
+      <c r="J9" s="48">
         <v>69</v>
       </c>
-      <c r="K9" s="42"/>
+      <c r="K9" s="6"/>
       <c r="L9" s="16">
-        <f t="shared" ref="L5:L68" si="3">J9</f>
+        <f t="shared" ref="L9:L62" si="3">J9</f>
         <v>69</v>
       </c>
       <c r="M9" s="17">
@@ -3771,11 +5439,11 @@
       </c>
     </row>
     <row r="10" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="48">
+      <c r="B10" s="42">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="37">
         <v>0</v>
       </c>
       <c r="D10" s="7">
@@ -3793,13 +5461,13 @@
       <c r="H10" s="7">
         <v>1</v>
       </c>
-      <c r="I10" s="55">
-        <v>0</v>
-      </c>
-      <c r="J10" s="57">
+      <c r="I10" s="46">
+        <v>0</v>
+      </c>
+      <c r="J10" s="48">
         <v>70</v>
       </c>
-      <c r="K10" s="42"/>
+      <c r="K10" s="6"/>
       <c r="L10" s="16">
         <f t="shared" si="3"/>
         <v>70</v>
@@ -3810,11 +5478,11 @@
       </c>
     </row>
     <row r="11" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="48">
+      <c r="B11" s="42">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="37">
         <v>0</v>
       </c>
       <c r="D11" s="7">
@@ -3832,13 +5500,13 @@
       <c r="H11" s="7">
         <v>1</v>
       </c>
-      <c r="I11" s="55">
-        <v>1</v>
-      </c>
-      <c r="J11" s="57">
+      <c r="I11" s="46">
+        <v>1</v>
+      </c>
+      <c r="J11" s="48">
         <v>71</v>
       </c>
-      <c r="K11" s="42"/>
+      <c r="K11" s="6"/>
       <c r="L11" s="16">
         <f t="shared" si="3"/>
         <v>71</v>
@@ -3849,11 +5517,11 @@
       </c>
     </row>
     <row r="12" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="48">
+      <c r="B12" s="42">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="37">
         <v>0</v>
       </c>
       <c r="D12" s="7">
@@ -3871,13 +5539,13 @@
       <c r="H12" s="7">
         <v>0</v>
       </c>
-      <c r="I12" s="55">
-        <v>0</v>
-      </c>
-      <c r="J12" s="57">
+      <c r="I12" s="46">
+        <v>0</v>
+      </c>
+      <c r="J12" s="48">
         <v>72</v>
       </c>
-      <c r="K12" s="42"/>
+      <c r="K12" s="6"/>
       <c r="L12" s="16">
         <f t="shared" si="3"/>
         <v>72</v>
@@ -3888,11 +5556,11 @@
       </c>
     </row>
     <row r="13" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B13" s="48">
+      <c r="B13" s="42">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="C13" s="40">
+      <c r="C13" s="37">
         <v>0</v>
       </c>
       <c r="D13" s="7">
@@ -3910,13 +5578,13 @@
       <c r="H13" s="7">
         <v>0</v>
       </c>
-      <c r="I13" s="55">
-        <v>1</v>
-      </c>
-      <c r="J13" s="57">
+      <c r="I13" s="46">
+        <v>1</v>
+      </c>
+      <c r="J13" s="48">
         <v>73</v>
       </c>
-      <c r="K13" s="42"/>
+      <c r="K13" s="6"/>
       <c r="L13" s="16">
         <f t="shared" si="3"/>
         <v>73</v>
@@ -3927,11 +5595,11 @@
       </c>
     </row>
     <row r="14" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="48">
+      <c r="B14" s="42">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="C14" s="40">
+      <c r="C14" s="37">
         <v>0</v>
       </c>
       <c r="D14" s="7">
@@ -3949,13 +5617,13 @@
       <c r="H14" s="7">
         <v>1</v>
       </c>
-      <c r="I14" s="55">
-        <v>0</v>
-      </c>
-      <c r="J14" s="57">
+      <c r="I14" s="46">
+        <v>0</v>
+      </c>
+      <c r="J14" s="48">
         <v>74</v>
       </c>
-      <c r="K14" s="42"/>
+      <c r="K14" s="6"/>
       <c r="L14" s="16">
         <f t="shared" si="3"/>
         <v>74</v>
@@ -3966,11 +5634,11 @@
       </c>
     </row>
     <row r="15" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="48">
+      <c r="B15" s="42">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="C15" s="40">
+      <c r="C15" s="37">
         <v>0</v>
       </c>
       <c r="D15" s="7">
@@ -3988,13 +5656,13 @@
       <c r="H15" s="7">
         <v>1</v>
       </c>
-      <c r="I15" s="55">
-        <v>1</v>
-      </c>
-      <c r="J15" s="57">
+      <c r="I15" s="46">
+        <v>1</v>
+      </c>
+      <c r="J15" s="48">
         <v>75</v>
       </c>
-      <c r="K15" s="42"/>
+      <c r="K15" s="6"/>
       <c r="L15" s="16">
         <f t="shared" si="3"/>
         <v>75</v>
@@ -4005,11 +5673,11 @@
       </c>
     </row>
     <row r="16" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="48">
+      <c r="B16" s="42">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="C16" s="40">
+      <c r="C16" s="37">
         <v>0</v>
       </c>
       <c r="D16" s="7">
@@ -4027,13 +5695,13 @@
       <c r="H16" s="7">
         <v>0</v>
       </c>
-      <c r="I16" s="55">
-        <v>0</v>
-      </c>
-      <c r="J16" s="57">
+      <c r="I16" s="46">
+        <v>0</v>
+      </c>
+      <c r="J16" s="48">
         <v>76</v>
       </c>
-      <c r="K16" s="42"/>
+      <c r="K16" s="6"/>
       <c r="L16" s="16">
         <f t="shared" si="3"/>
         <v>76</v>
@@ -4044,11 +5712,11 @@
       </c>
     </row>
     <row r="17" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="48">
+      <c r="B17" s="42">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="C17" s="40">
+      <c r="C17" s="37">
         <v>0</v>
       </c>
       <c r="D17" s="7">
@@ -4066,13 +5734,13 @@
       <c r="H17" s="7">
         <v>0</v>
       </c>
-      <c r="I17" s="55">
-        <v>1</v>
-      </c>
-      <c r="J17" s="57">
+      <c r="I17" s="46">
+        <v>1</v>
+      </c>
+      <c r="J17" s="48">
         <v>77</v>
       </c>
-      <c r="K17" s="42"/>
+      <c r="K17" s="6"/>
       <c r="L17" s="16">
         <f t="shared" si="3"/>
         <v>77</v>
@@ -4083,11 +5751,11 @@
       </c>
     </row>
     <row r="18" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="48">
+      <c r="B18" s="42">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="C18" s="40">
+      <c r="C18" s="37">
         <v>0</v>
       </c>
       <c r="D18" s="7">
@@ -4105,13 +5773,13 @@
       <c r="H18" s="7">
         <v>1</v>
       </c>
-      <c r="I18" s="55">
-        <v>0</v>
-      </c>
-      <c r="J18" s="57">
+      <c r="I18" s="46">
+        <v>0</v>
+      </c>
+      <c r="J18" s="48">
         <v>78</v>
       </c>
-      <c r="K18" s="42"/>
+      <c r="K18" s="6"/>
       <c r="L18" s="16">
         <f t="shared" si="3"/>
         <v>78</v>
@@ -4122,11 +5790,11 @@
       </c>
     </row>
     <row r="19" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="48">
+      <c r="B19" s="42">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="C19" s="40">
+      <c r="C19" s="37">
         <v>0</v>
       </c>
       <c r="D19" s="7">
@@ -4144,13 +5812,13 @@
       <c r="H19" s="7">
         <v>1</v>
       </c>
-      <c r="I19" s="55">
-        <v>1</v>
-      </c>
-      <c r="J19" s="57">
+      <c r="I19" s="46">
+        <v>1</v>
+      </c>
+      <c r="J19" s="48">
         <v>79</v>
       </c>
-      <c r="K19" s="42"/>
+      <c r="K19" s="6"/>
       <c r="L19" s="16">
         <f t="shared" si="3"/>
         <v>79</v>
@@ -4161,11 +5829,11 @@
       </c>
     </row>
     <row r="20" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="48">
+      <c r="B20" s="42">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="C20" s="40">
+      <c r="C20" s="37">
         <v>0</v>
       </c>
       <c r="D20" s="7">
@@ -4183,13 +5851,13 @@
       <c r="H20" s="7">
         <v>0</v>
       </c>
-      <c r="I20" s="55">
-        <v>0</v>
-      </c>
-      <c r="J20" s="57">
+      <c r="I20" s="46">
+        <v>0</v>
+      </c>
+      <c r="J20" s="48">
         <v>80</v>
       </c>
-      <c r="K20" s="42"/>
+      <c r="K20" s="6"/>
       <c r="L20" s="16">
         <f t="shared" si="3"/>
         <v>80</v>
@@ -4200,11 +5868,11 @@
       </c>
     </row>
     <row r="21" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="48">
+      <c r="B21" s="42">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="C21" s="40">
+      <c r="C21" s="37">
         <v>0</v>
       </c>
       <c r="D21" s="7">
@@ -4222,13 +5890,13 @@
       <c r="H21" s="7">
         <v>0</v>
       </c>
-      <c r="I21" s="55">
-        <v>1</v>
-      </c>
-      <c r="J21" s="57">
+      <c r="I21" s="46">
+        <v>1</v>
+      </c>
+      <c r="J21" s="48">
         <v>81</v>
       </c>
-      <c r="K21" s="42"/>
+      <c r="K21" s="6"/>
       <c r="L21" s="16">
         <f t="shared" si="3"/>
         <v>81</v>
@@ -4239,11 +5907,11 @@
       </c>
     </row>
     <row r="22" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B22" s="48">
+      <c r="B22" s="42">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="C22" s="40">
+      <c r="C22" s="37">
         <v>0</v>
       </c>
       <c r="D22" s="7">
@@ -4261,13 +5929,13 @@
       <c r="H22" s="7">
         <v>1</v>
       </c>
-      <c r="I22" s="55">
-        <v>0</v>
-      </c>
-      <c r="J22" s="57">
+      <c r="I22" s="46">
+        <v>0</v>
+      </c>
+      <c r="J22" s="48">
         <v>82</v>
       </c>
-      <c r="K22" s="42"/>
+      <c r="K22" s="6"/>
       <c r="L22" s="16">
         <f t="shared" si="3"/>
         <v>82</v>
@@ -4278,11 +5946,11 @@
       </c>
     </row>
     <row r="23" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B23" s="48">
+      <c r="B23" s="42">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="C23" s="40">
+      <c r="C23" s="37">
         <v>0</v>
       </c>
       <c r="D23" s="7">
@@ -4300,13 +5968,13 @@
       <c r="H23" s="7">
         <v>1</v>
       </c>
-      <c r="I23" s="55">
-        <v>1</v>
-      </c>
-      <c r="J23" s="57">
+      <c r="I23" s="46">
+        <v>1</v>
+      </c>
+      <c r="J23" s="48">
         <v>83</v>
       </c>
-      <c r="K23" s="42"/>
+      <c r="K23" s="6"/>
       <c r="L23" s="16">
         <f t="shared" si="3"/>
         <v>83</v>
@@ -4317,11 +5985,11 @@
       </c>
     </row>
     <row r="24" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B24" s="48">
+      <c r="B24" s="42">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="C24" s="40">
+      <c r="C24" s="37">
         <v>0</v>
       </c>
       <c r="D24" s="7">
@@ -4339,13 +6007,13 @@
       <c r="H24" s="7">
         <v>0</v>
       </c>
-      <c r="I24" s="55">
-        <v>0</v>
-      </c>
-      <c r="J24" s="57">
+      <c r="I24" s="46">
+        <v>0</v>
+      </c>
+      <c r="J24" s="48">
         <v>84</v>
       </c>
-      <c r="K24" s="42"/>
+      <c r="K24" s="6"/>
       <c r="L24" s="16">
         <f t="shared" si="3"/>
         <v>84</v>
@@ -4356,11 +6024,11 @@
       </c>
     </row>
     <row r="25" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B25" s="48">
+      <c r="B25" s="42">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="C25" s="40">
+      <c r="C25" s="37">
         <v>0</v>
       </c>
       <c r="D25" s="7">
@@ -4378,13 +6046,13 @@
       <c r="H25" s="7">
         <v>0</v>
       </c>
-      <c r="I25" s="55">
-        <v>1</v>
-      </c>
-      <c r="J25" s="57">
+      <c r="I25" s="46">
+        <v>1</v>
+      </c>
+      <c r="J25" s="48">
         <v>85</v>
       </c>
-      <c r="K25" s="42"/>
+      <c r="K25" s="6"/>
       <c r="L25" s="16">
         <f t="shared" si="3"/>
         <v>85</v>
@@ -4395,11 +6063,11 @@
       </c>
     </row>
     <row r="26" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B26" s="48">
+      <c r="B26" s="42">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="C26" s="40">
+      <c r="C26" s="37">
         <v>0</v>
       </c>
       <c r="D26" s="7">
@@ -4417,13 +6085,13 @@
       <c r="H26" s="7">
         <v>1</v>
       </c>
-      <c r="I26" s="55">
-        <v>0</v>
-      </c>
-      <c r="J26" s="57">
+      <c r="I26" s="46">
+        <v>0</v>
+      </c>
+      <c r="J26" s="48">
         <v>86</v>
       </c>
-      <c r="K26" s="42"/>
+      <c r="K26" s="6"/>
       <c r="L26" s="16">
         <f t="shared" si="3"/>
         <v>86</v>
@@ -4434,11 +6102,11 @@
       </c>
     </row>
     <row r="27" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B27" s="48">
+      <c r="B27" s="42">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="C27" s="40">
+      <c r="C27" s="37">
         <v>0</v>
       </c>
       <c r="D27" s="7">
@@ -4456,13 +6124,13 @@
       <c r="H27" s="7">
         <v>1</v>
       </c>
-      <c r="I27" s="55">
-        <v>1</v>
-      </c>
-      <c r="J27" s="57">
+      <c r="I27" s="46">
+        <v>1</v>
+      </c>
+      <c r="J27" s="48">
         <v>87</v>
       </c>
-      <c r="K27" s="42"/>
+      <c r="K27" s="6"/>
       <c r="L27" s="16">
         <f t="shared" si="3"/>
         <v>87</v>
@@ -4473,11 +6141,11 @@
       </c>
     </row>
     <row r="28" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B28" s="48">
+      <c r="B28" s="42">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="C28" s="40">
+      <c r="C28" s="37">
         <v>0</v>
       </c>
       <c r="D28" s="7">
@@ -4495,13 +6163,13 @@
       <c r="H28" s="7">
         <v>0</v>
       </c>
-      <c r="I28" s="55">
-        <v>0</v>
-      </c>
-      <c r="J28" s="57">
+      <c r="I28" s="46">
+        <v>0</v>
+      </c>
+      <c r="J28" s="48">
         <v>88</v>
       </c>
-      <c r="K28" s="42"/>
+      <c r="K28" s="6"/>
       <c r="L28" s="16">
         <f t="shared" si="3"/>
         <v>88</v>
@@ -4512,11 +6180,11 @@
       </c>
     </row>
     <row r="29" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B29" s="48">
+      <c r="B29" s="42">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="C29" s="40">
+      <c r="C29" s="37">
         <v>0</v>
       </c>
       <c r="D29" s="7">
@@ -4534,13 +6202,13 @@
       <c r="H29" s="7">
         <v>0</v>
       </c>
-      <c r="I29" s="55">
-        <v>1</v>
-      </c>
-      <c r="J29" s="57">
+      <c r="I29" s="46">
+        <v>1</v>
+      </c>
+      <c r="J29" s="48">
         <v>89</v>
       </c>
-      <c r="K29" s="42"/>
+      <c r="K29" s="6"/>
       <c r="L29" s="16">
         <f t="shared" si="3"/>
         <v>89</v>
@@ -4551,11 +6219,11 @@
       </c>
     </row>
     <row r="30" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B30" s="48">
+      <c r="B30" s="42">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="C30" s="40">
+      <c r="C30" s="37">
         <v>0</v>
       </c>
       <c r="D30" s="7">
@@ -4573,13 +6241,13 @@
       <c r="H30" s="7">
         <v>1</v>
       </c>
-      <c r="I30" s="55">
-        <v>0</v>
-      </c>
-      <c r="J30" s="57">
+      <c r="I30" s="46">
+        <v>0</v>
+      </c>
+      <c r="J30" s="48">
         <v>90</v>
       </c>
-      <c r="K30" s="42"/>
+      <c r="K30" s="6"/>
       <c r="L30" s="16">
         <f t="shared" si="3"/>
         <v>90</v>
@@ -4590,11 +6258,11 @@
       </c>
     </row>
     <row r="31" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B31" s="48">
+      <c r="B31" s="42">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="C31" s="40">
+      <c r="C31" s="37">
         <v>0</v>
       </c>
       <c r="D31" s="7">
@@ -4612,13 +6280,13 @@
       <c r="H31" s="7">
         <v>1</v>
       </c>
-      <c r="I31" s="55">
-        <v>1</v>
-      </c>
-      <c r="J31" s="57">
+      <c r="I31" s="46">
+        <v>1</v>
+      </c>
+      <c r="J31" s="48">
         <v>91</v>
       </c>
-      <c r="K31" s="42"/>
+      <c r="K31" s="6"/>
       <c r="L31" s="16">
         <f t="shared" si="3"/>
         <v>91</v>
@@ -4629,11 +6297,11 @@
       </c>
     </row>
     <row r="32" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B32" s="48">
+      <c r="B32" s="42">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="C32" s="40">
+      <c r="C32" s="37">
         <v>0</v>
       </c>
       <c r="D32" s="7">
@@ -4651,13 +6319,13 @@
       <c r="H32" s="7">
         <v>0</v>
       </c>
-      <c r="I32" s="55">
-        <v>0</v>
-      </c>
-      <c r="J32" s="57">
+      <c r="I32" s="46">
+        <v>0</v>
+      </c>
+      <c r="J32" s="48">
         <v>92</v>
       </c>
-      <c r="K32" s="42"/>
+      <c r="K32" s="6"/>
       <c r="L32" s="16">
         <f t="shared" si="3"/>
         <v>92</v>
@@ -4668,11 +6336,11 @@
       </c>
     </row>
     <row r="33" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B33" s="48">
+      <c r="B33" s="42">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="C33" s="40">
+      <c r="C33" s="37">
         <v>0</v>
       </c>
       <c r="D33" s="7">
@@ -4690,13 +6358,13 @@
       <c r="H33" s="7">
         <v>0</v>
       </c>
-      <c r="I33" s="55">
-        <v>1</v>
-      </c>
-      <c r="J33" s="57">
+      <c r="I33" s="46">
+        <v>1</v>
+      </c>
+      <c r="J33" s="48">
         <v>93</v>
       </c>
-      <c r="K33" s="42"/>
+      <c r="K33" s="6"/>
       <c r="L33" s="16">
         <f t="shared" si="3"/>
         <v>93</v>
@@ -4707,11 +6375,11 @@
       </c>
     </row>
     <row r="34" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B34" s="48">
+      <c r="B34" s="42">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="C34" s="40">
+      <c r="C34" s="37">
         <v>0</v>
       </c>
       <c r="D34" s="7">
@@ -4729,13 +6397,13 @@
       <c r="H34" s="7">
         <v>1</v>
       </c>
-      <c r="I34" s="55">
-        <v>0</v>
-      </c>
-      <c r="J34" s="57">
+      <c r="I34" s="46">
+        <v>0</v>
+      </c>
+      <c r="J34" s="48">
         <v>94</v>
       </c>
-      <c r="K34" s="42"/>
+      <c r="K34" s="6"/>
       <c r="L34" s="16">
         <f t="shared" si="3"/>
         <v>94</v>
@@ -4746,11 +6414,11 @@
       </c>
     </row>
     <row r="35" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B35" s="48">
+      <c r="B35" s="42">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="C35" s="40">
+      <c r="C35" s="37">
         <v>0</v>
       </c>
       <c r="D35" s="7">
@@ -4768,13 +6436,13 @@
       <c r="H35" s="7">
         <v>1</v>
       </c>
-      <c r="I35" s="55">
-        <v>1</v>
-      </c>
-      <c r="J35" s="57">
+      <c r="I35" s="46">
+        <v>1</v>
+      </c>
+      <c r="J35" s="48">
         <v>95</v>
       </c>
-      <c r="K35" s="42"/>
+      <c r="K35" s="6"/>
       <c r="L35" s="16">
         <f t="shared" si="3"/>
         <v>95</v>
@@ -4785,11 +6453,11 @@
       </c>
     </row>
     <row r="36" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B36" s="48">
+      <c r="B36" s="42">
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
-      <c r="C36" s="40">
+      <c r="C36" s="37">
         <v>0</v>
       </c>
       <c r="D36" s="7">
@@ -4807,13 +6475,13 @@
       <c r="H36" s="7">
         <v>0</v>
       </c>
-      <c r="I36" s="55">
-        <v>0</v>
-      </c>
-      <c r="J36" s="57">
+      <c r="I36" s="46">
+        <v>0</v>
+      </c>
+      <c r="J36" s="48">
         <v>96</v>
       </c>
-      <c r="K36" s="42"/>
+      <c r="K36" s="6"/>
       <c r="L36" s="16">
         <f t="shared" si="3"/>
         <v>96</v>
@@ -4824,11 +6492,11 @@
       </c>
     </row>
     <row r="37" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B37" s="48">
+      <c r="B37" s="42">
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="C37" s="40">
+      <c r="C37" s="37">
         <v>0</v>
       </c>
       <c r="D37" s="7">
@@ -4846,13 +6514,13 @@
       <c r="H37" s="7">
         <v>0</v>
       </c>
-      <c r="I37" s="55">
-        <v>1</v>
-      </c>
-      <c r="J37" s="57">
+      <c r="I37" s="46">
+        <v>1</v>
+      </c>
+      <c r="J37" s="48">
         <v>97</v>
       </c>
-      <c r="K37" s="42"/>
+      <c r="K37" s="6"/>
       <c r="L37" s="16">
         <f t="shared" si="3"/>
         <v>97</v>
@@ -4863,11 +6531,11 @@
       </c>
     </row>
     <row r="38" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B38" s="48">
+      <c r="B38" s="42">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="C38" s="40">
+      <c r="C38" s="37">
         <v>0</v>
       </c>
       <c r="D38" s="7">
@@ -4885,13 +6553,13 @@
       <c r="H38" s="7">
         <v>1</v>
       </c>
-      <c r="I38" s="55">
-        <v>0</v>
-      </c>
-      <c r="J38" s="57">
+      <c r="I38" s="46">
+        <v>0</v>
+      </c>
+      <c r="J38" s="48">
         <v>98</v>
       </c>
-      <c r="K38" s="42"/>
+      <c r="K38" s="6"/>
       <c r="L38" s="16">
         <f t="shared" si="3"/>
         <v>98</v>
@@ -4902,11 +6570,11 @@
       </c>
     </row>
     <row r="39" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B39" s="48">
+      <c r="B39" s="42">
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="C39" s="40">
+      <c r="C39" s="37">
         <v>0</v>
       </c>
       <c r="D39" s="7">
@@ -4924,13 +6592,13 @@
       <c r="H39" s="7">
         <v>1</v>
       </c>
-      <c r="I39" s="55">
-        <v>1</v>
-      </c>
-      <c r="J39" s="57">
+      <c r="I39" s="46">
+        <v>1</v>
+      </c>
+      <c r="J39" s="48">
         <v>99</v>
       </c>
-      <c r="K39" s="42"/>
+      <c r="K39" s="6"/>
       <c r="L39" s="16">
         <f t="shared" si="3"/>
         <v>99</v>
@@ -4941,11 +6609,11 @@
       </c>
     </row>
     <row r="40" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B40" s="48">
+      <c r="B40" s="42">
         <f t="shared" si="2"/>
         <v>36</v>
       </c>
-      <c r="C40" s="40">
+      <c r="C40" s="37">
         <v>0</v>
       </c>
       <c r="D40" s="7">
@@ -4963,13 +6631,13 @@
       <c r="H40" s="7">
         <v>0</v>
       </c>
-      <c r="I40" s="55">
-        <v>0</v>
-      </c>
-      <c r="J40" s="57">
+      <c r="I40" s="46">
+        <v>0</v>
+      </c>
+      <c r="J40" s="48">
         <v>100</v>
       </c>
-      <c r="K40" s="42"/>
+      <c r="K40" s="6"/>
       <c r="L40" s="16">
         <f t="shared" si="3"/>
         <v>100</v>
@@ -4980,11 +6648,11 @@
       </c>
     </row>
     <row r="41" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B41" s="48">
+      <c r="B41" s="42">
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="C41" s="40">
+      <c r="C41" s="37">
         <v>0</v>
       </c>
       <c r="D41" s="7">
@@ -5002,13 +6670,13 @@
       <c r="H41" s="7">
         <v>0</v>
       </c>
-      <c r="I41" s="55">
-        <v>1</v>
-      </c>
-      <c r="J41" s="57">
+      <c r="I41" s="46">
+        <v>1</v>
+      </c>
+      <c r="J41" s="48">
         <v>101</v>
       </c>
-      <c r="K41" s="42"/>
+      <c r="K41" s="6"/>
       <c r="L41" s="16">
         <f t="shared" si="3"/>
         <v>101</v>
@@ -5019,11 +6687,11 @@
       </c>
     </row>
     <row r="42" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B42" s="48">
+      <c r="B42" s="42">
         <f t="shared" si="2"/>
         <v>38</v>
       </c>
-      <c r="C42" s="40">
+      <c r="C42" s="37">
         <v>0</v>
       </c>
       <c r="D42" s="7">
@@ -5041,13 +6709,13 @@
       <c r="H42" s="7">
         <v>1</v>
       </c>
-      <c r="I42" s="55">
-        <v>0</v>
-      </c>
-      <c r="J42" s="57">
+      <c r="I42" s="46">
+        <v>0</v>
+      </c>
+      <c r="J42" s="48">
         <v>102</v>
       </c>
-      <c r="K42" s="42"/>
+      <c r="K42" s="6"/>
       <c r="L42" s="16">
         <f t="shared" si="3"/>
         <v>102</v>
@@ -5058,11 +6726,11 @@
       </c>
     </row>
     <row r="43" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B43" s="48">
+      <c r="B43" s="42">
         <f t="shared" si="2"/>
         <v>39</v>
       </c>
-      <c r="C43" s="40">
+      <c r="C43" s="37">
         <v>0</v>
       </c>
       <c r="D43" s="7">
@@ -5080,13 +6748,13 @@
       <c r="H43" s="7">
         <v>1</v>
       </c>
-      <c r="I43" s="55">
-        <v>1</v>
-      </c>
-      <c r="J43" s="57">
+      <c r="I43" s="46">
+        <v>1</v>
+      </c>
+      <c r="J43" s="48">
         <v>103</v>
       </c>
-      <c r="K43" s="42"/>
+      <c r="K43" s="6"/>
       <c r="L43" s="16">
         <f t="shared" si="3"/>
         <v>103</v>
@@ -5097,11 +6765,11 @@
       </c>
     </row>
     <row r="44" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B44" s="48">
+      <c r="B44" s="42">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="C44" s="40">
+      <c r="C44" s="37">
         <v>0</v>
       </c>
       <c r="D44" s="7">
@@ -5119,13 +6787,13 @@
       <c r="H44" s="7">
         <v>0</v>
       </c>
-      <c r="I44" s="55">
-        <v>0</v>
-      </c>
-      <c r="J44" s="57">
+      <c r="I44" s="46">
+        <v>0</v>
+      </c>
+      <c r="J44" s="48">
         <v>104</v>
       </c>
-      <c r="K44" s="42"/>
+      <c r="K44" s="6"/>
       <c r="L44" s="16">
         <f t="shared" si="3"/>
         <v>104</v>
@@ -5136,11 +6804,11 @@
       </c>
     </row>
     <row r="45" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B45" s="48">
+      <c r="B45" s="42">
         <f t="shared" si="2"/>
         <v>41</v>
       </c>
-      <c r="C45" s="40">
+      <c r="C45" s="37">
         <v>0</v>
       </c>
       <c r="D45" s="7">
@@ -5158,13 +6826,13 @@
       <c r="H45" s="7">
         <v>0</v>
       </c>
-      <c r="I45" s="55">
-        <v>1</v>
-      </c>
-      <c r="J45" s="57">
+      <c r="I45" s="46">
+        <v>1</v>
+      </c>
+      <c r="J45" s="48">
         <v>105</v>
       </c>
-      <c r="K45" s="42"/>
+      <c r="K45" s="6"/>
       <c r="L45" s="16">
         <f t="shared" si="3"/>
         <v>105</v>
@@ -5175,11 +6843,11 @@
       </c>
     </row>
     <row r="46" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B46" s="48">
+      <c r="B46" s="42">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="C46" s="40">
+      <c r="C46" s="37">
         <v>0</v>
       </c>
       <c r="D46" s="7">
@@ -5197,13 +6865,13 @@
       <c r="H46" s="7">
         <v>1</v>
       </c>
-      <c r="I46" s="55">
-        <v>0</v>
-      </c>
-      <c r="J46" s="57">
+      <c r="I46" s="46">
+        <v>0</v>
+      </c>
+      <c r="J46" s="48">
         <v>106</v>
       </c>
-      <c r="K46" s="42"/>
+      <c r="K46" s="6"/>
       <c r="L46" s="16">
         <f t="shared" si="3"/>
         <v>106</v>
@@ -5214,11 +6882,11 @@
       </c>
     </row>
     <row r="47" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B47" s="48">
+      <c r="B47" s="42">
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="C47" s="40">
+      <c r="C47" s="37">
         <v>0</v>
       </c>
       <c r="D47" s="7">
@@ -5236,13 +6904,13 @@
       <c r="H47" s="7">
         <v>1</v>
       </c>
-      <c r="I47" s="55">
-        <v>1</v>
-      </c>
-      <c r="J47" s="57">
+      <c r="I47" s="46">
+        <v>1</v>
+      </c>
+      <c r="J47" s="48">
         <v>107</v>
       </c>
-      <c r="K47" s="42"/>
+      <c r="K47" s="6"/>
       <c r="L47" s="16">
         <f t="shared" si="3"/>
         <v>107</v>
@@ -5253,11 +6921,11 @@
       </c>
     </row>
     <row r="48" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B48" s="48">
+      <c r="B48" s="42">
         <f t="shared" si="2"/>
         <v>44</v>
       </c>
-      <c r="C48" s="40">
+      <c r="C48" s="37">
         <v>0</v>
       </c>
       <c r="D48" s="7">
@@ -5275,13 +6943,13 @@
       <c r="H48" s="7">
         <v>0</v>
       </c>
-      <c r="I48" s="55">
-        <v>0</v>
-      </c>
-      <c r="J48" s="57">
+      <c r="I48" s="46">
+        <v>0</v>
+      </c>
+      <c r="J48" s="48">
         <v>108</v>
       </c>
-      <c r="K48" s="42"/>
+      <c r="K48" s="6"/>
       <c r="L48" s="16">
         <f t="shared" si="3"/>
         <v>108</v>
@@ -5292,11 +6960,11 @@
       </c>
     </row>
     <row r="49" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B49" s="48">
+      <c r="B49" s="42">
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="C49" s="40">
+      <c r="C49" s="37">
         <v>0</v>
       </c>
       <c r="D49" s="7">
@@ -5314,13 +6982,13 @@
       <c r="H49" s="7">
         <v>0</v>
       </c>
-      <c r="I49" s="55">
-        <v>1</v>
-      </c>
-      <c r="J49" s="57">
+      <c r="I49" s="46">
+        <v>1</v>
+      </c>
+      <c r="J49" s="48">
         <v>109</v>
       </c>
-      <c r="K49" s="42"/>
+      <c r="K49" s="6"/>
       <c r="L49" s="16">
         <f t="shared" si="3"/>
         <v>109</v>
@@ -5331,11 +6999,11 @@
       </c>
     </row>
     <row r="50" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B50" s="48">
+      <c r="B50" s="42">
         <f t="shared" si="2"/>
         <v>46</v>
       </c>
-      <c r="C50" s="40">
+      <c r="C50" s="37">
         <v>0</v>
       </c>
       <c r="D50" s="7">
@@ -5353,13 +7021,13 @@
       <c r="H50" s="7">
         <v>1</v>
       </c>
-      <c r="I50" s="55">
-        <v>0</v>
-      </c>
-      <c r="J50" s="57">
+      <c r="I50" s="46">
+        <v>0</v>
+      </c>
+      <c r="J50" s="48">
         <v>110</v>
       </c>
-      <c r="K50" s="42"/>
+      <c r="K50" s="6"/>
       <c r="L50" s="16">
         <f t="shared" si="3"/>
         <v>110</v>
@@ -5370,11 +7038,11 @@
       </c>
     </row>
     <row r="51" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B51" s="48">
+      <c r="B51" s="42">
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="C51" s="40">
+      <c r="C51" s="37">
         <v>0</v>
       </c>
       <c r="D51" s="7">
@@ -5392,13 +7060,13 @@
       <c r="H51" s="7">
         <v>1</v>
       </c>
-      <c r="I51" s="55">
-        <v>1</v>
-      </c>
-      <c r="J51" s="57">
+      <c r="I51" s="46">
+        <v>1</v>
+      </c>
+      <c r="J51" s="48">
         <v>111</v>
       </c>
-      <c r="K51" s="42"/>
+      <c r="K51" s="6"/>
       <c r="L51" s="16">
         <f t="shared" si="3"/>
         <v>111</v>
@@ -5409,11 +7077,11 @@
       </c>
     </row>
     <row r="52" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B52" s="48">
+      <c r="B52" s="42">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="C52" s="40">
+      <c r="C52" s="37">
         <v>0</v>
       </c>
       <c r="D52" s="7">
@@ -5431,13 +7099,13 @@
       <c r="H52" s="7">
         <v>0</v>
       </c>
-      <c r="I52" s="55">
-        <v>0</v>
-      </c>
-      <c r="J52" s="57">
+      <c r="I52" s="46">
+        <v>0</v>
+      </c>
+      <c r="J52" s="48">
         <v>112</v>
       </c>
-      <c r="K52" s="42"/>
+      <c r="K52" s="6"/>
       <c r="L52" s="16">
         <f t="shared" si="3"/>
         <v>112</v>
@@ -5448,11 +7116,11 @@
       </c>
     </row>
     <row r="53" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B53" s="48">
+      <c r="B53" s="42">
         <f t="shared" si="2"/>
         <v>49</v>
       </c>
-      <c r="C53" s="40">
+      <c r="C53" s="37">
         <v>0</v>
       </c>
       <c r="D53" s="7">
@@ -5470,13 +7138,13 @@
       <c r="H53" s="7">
         <v>0</v>
       </c>
-      <c r="I53" s="55">
-        <v>1</v>
-      </c>
-      <c r="J53" s="57">
+      <c r="I53" s="46">
+        <v>1</v>
+      </c>
+      <c r="J53" s="48">
         <v>113</v>
       </c>
-      <c r="K53" s="42"/>
+      <c r="K53" s="6"/>
       <c r="L53" s="16">
         <f t="shared" si="3"/>
         <v>113</v>
@@ -5487,11 +7155,11 @@
       </c>
     </row>
     <row r="54" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B54" s="48">
+      <c r="B54" s="42">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="C54" s="40">
+      <c r="C54" s="37">
         <v>0</v>
       </c>
       <c r="D54" s="7">
@@ -5509,13 +7177,13 @@
       <c r="H54" s="7">
         <v>1</v>
       </c>
-      <c r="I54" s="55">
-        <v>0</v>
-      </c>
-      <c r="J54" s="57">
+      <c r="I54" s="46">
+        <v>0</v>
+      </c>
+      <c r="J54" s="48">
         <v>114</v>
       </c>
-      <c r="K54" s="42"/>
+      <c r="K54" s="6"/>
       <c r="L54" s="16">
         <f t="shared" si="3"/>
         <v>114</v>
@@ -5526,11 +7194,11 @@
       </c>
     </row>
     <row r="55" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B55" s="48">
+      <c r="B55" s="42">
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="C55" s="40">
+      <c r="C55" s="37">
         <v>0</v>
       </c>
       <c r="D55" s="7">
@@ -5548,13 +7216,13 @@
       <c r="H55" s="7">
         <v>1</v>
       </c>
-      <c r="I55" s="55">
-        <v>1</v>
-      </c>
-      <c r="J55" s="57">
+      <c r="I55" s="46">
+        <v>1</v>
+      </c>
+      <c r="J55" s="48">
         <v>115</v>
       </c>
-      <c r="K55" s="42"/>
+      <c r="K55" s="6"/>
       <c r="L55" s="16">
         <f t="shared" si="3"/>
         <v>115</v>
@@ -5565,11 +7233,11 @@
       </c>
     </row>
     <row r="56" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B56" s="48">
+      <c r="B56" s="42">
         <f t="shared" si="2"/>
         <v>52</v>
       </c>
-      <c r="C56" s="40">
+      <c r="C56" s="37">
         <v>0</v>
       </c>
       <c r="D56" s="7">
@@ -5587,13 +7255,13 @@
       <c r="H56" s="7">
         <v>0</v>
       </c>
-      <c r="I56" s="55">
-        <v>0</v>
-      </c>
-      <c r="J56" s="57">
+      <c r="I56" s="46">
+        <v>0</v>
+      </c>
+      <c r="J56" s="48">
         <v>116</v>
       </c>
-      <c r="K56" s="42"/>
+      <c r="K56" s="6"/>
       <c r="L56" s="16">
         <f t="shared" si="3"/>
         <v>116</v>
@@ -5604,11 +7272,11 @@
       </c>
     </row>
     <row r="57" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B57" s="48">
+      <c r="B57" s="42">
         <f t="shared" si="2"/>
         <v>53</v>
       </c>
-      <c r="C57" s="40">
+      <c r="C57" s="37">
         <v>0</v>
       </c>
       <c r="D57" s="7">
@@ -5626,13 +7294,13 @@
       <c r="H57" s="7">
         <v>0</v>
       </c>
-      <c r="I57" s="55">
-        <v>1</v>
-      </c>
-      <c r="J57" s="57">
+      <c r="I57" s="46">
+        <v>1</v>
+      </c>
+      <c r="J57" s="48">
         <v>117</v>
       </c>
-      <c r="K57" s="42"/>
+      <c r="K57" s="6"/>
       <c r="L57" s="16">
         <f t="shared" si="3"/>
         <v>117</v>
@@ -5643,11 +7311,11 @@
       </c>
     </row>
     <row r="58" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B58" s="48">
+      <c r="B58" s="42">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="C58" s="40">
+      <c r="C58" s="37">
         <v>0</v>
       </c>
       <c r="D58" s="7">
@@ -5665,13 +7333,13 @@
       <c r="H58" s="7">
         <v>1</v>
       </c>
-      <c r="I58" s="55">
-        <v>0</v>
-      </c>
-      <c r="J58" s="57">
+      <c r="I58" s="46">
+        <v>0</v>
+      </c>
+      <c r="J58" s="48">
         <v>118</v>
       </c>
-      <c r="K58" s="42"/>
+      <c r="K58" s="6"/>
       <c r="L58" s="16">
         <f t="shared" si="3"/>
         <v>118</v>
@@ -5682,11 +7350,11 @@
       </c>
     </row>
     <row r="59" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B59" s="48">
+      <c r="B59" s="42">
         <f t="shared" si="2"/>
         <v>55</v>
       </c>
-      <c r="C59" s="40">
+      <c r="C59" s="37">
         <v>0</v>
       </c>
       <c r="D59" s="7">
@@ -5704,13 +7372,13 @@
       <c r="H59" s="7">
         <v>1</v>
       </c>
-      <c r="I59" s="55">
-        <v>1</v>
-      </c>
-      <c r="J59" s="57">
+      <c r="I59" s="46">
+        <v>1</v>
+      </c>
+      <c r="J59" s="48">
         <v>119</v>
       </c>
-      <c r="K59" s="42"/>
+      <c r="K59" s="6"/>
       <c r="L59" s="16">
         <f t="shared" si="3"/>
         <v>119</v>
@@ -5721,11 +7389,11 @@
       </c>
     </row>
     <row r="60" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B60" s="48">
+      <c r="B60" s="42">
         <f t="shared" si="2"/>
         <v>56</v>
       </c>
-      <c r="C60" s="40">
+      <c r="C60" s="37">
         <v>0</v>
       </c>
       <c r="D60" s="7">
@@ -5743,13 +7411,13 @@
       <c r="H60" s="7">
         <v>0</v>
       </c>
-      <c r="I60" s="55">
-        <v>0</v>
-      </c>
-      <c r="J60" s="57">
+      <c r="I60" s="46">
+        <v>0</v>
+      </c>
+      <c r="J60" s="48">
         <v>120</v>
       </c>
-      <c r="K60" s="42"/>
+      <c r="K60" s="6"/>
       <c r="L60" s="16">
         <f t="shared" si="3"/>
         <v>120</v>
@@ -5760,11 +7428,11 @@
       </c>
     </row>
     <row r="61" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B61" s="48">
+      <c r="B61" s="42">
         <f t="shared" si="2"/>
         <v>57</v>
       </c>
-      <c r="C61" s="40">
+      <c r="C61" s="37">
         <v>0</v>
       </c>
       <c r="D61" s="7">
@@ -5782,13 +7450,13 @@
       <c r="H61" s="7">
         <v>0</v>
       </c>
-      <c r="I61" s="55">
-        <v>1</v>
-      </c>
-      <c r="J61" s="57">
+      <c r="I61" s="46">
+        <v>1</v>
+      </c>
+      <c r="J61" s="48">
         <v>121</v>
       </c>
-      <c r="K61" s="42"/>
+      <c r="K61" s="6"/>
       <c r="L61" s="16">
         <f t="shared" si="3"/>
         <v>121</v>
@@ -5799,11 +7467,11 @@
       </c>
     </row>
     <row r="62" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B62" s="48">
+      <c r="B62" s="42">
         <f t="shared" si="2"/>
         <v>58</v>
       </c>
-      <c r="C62" s="40">
+      <c r="C62" s="37">
         <v>0</v>
       </c>
       <c r="D62" s="7">
@@ -5821,13 +7489,13 @@
       <c r="H62" s="7">
         <v>1</v>
       </c>
-      <c r="I62" s="55">
-        <v>0</v>
-      </c>
-      <c r="J62" s="57">
+      <c r="I62" s="46">
+        <v>0</v>
+      </c>
+      <c r="J62" s="48">
         <v>122</v>
       </c>
-      <c r="K62" s="42"/>
+      <c r="K62" s="6"/>
       <c r="L62" s="16">
         <f t="shared" si="3"/>
         <v>122</v>
@@ -5838,11 +7506,11 @@
       </c>
     </row>
     <row r="63" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B63" s="48">
+      <c r="B63" s="42">
         <f t="shared" si="2"/>
         <v>59</v>
       </c>
-      <c r="C63" s="40">
+      <c r="C63" s="37">
         <v>0</v>
       </c>
       <c r="D63" s="7">
@@ -5860,13 +7528,13 @@
       <c r="H63" s="7">
         <v>1</v>
       </c>
-      <c r="I63" s="55">
-        <v>1</v>
-      </c>
-      <c r="J63" s="57">
+      <c r="I63" s="46">
+        <v>1</v>
+      </c>
+      <c r="J63" s="48">
         <v>123</v>
       </c>
-      <c r="K63" s="42"/>
+      <c r="K63" s="6"/>
       <c r="L63" s="16">
         <v>59</v>
       </c>
@@ -5876,11 +7544,11 @@
       </c>
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B64" s="48">
+      <c r="B64" s="42">
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="C64" s="40">
+      <c r="C64" s="37">
         <v>0</v>
       </c>
       <c r="D64" s="7">
@@ -5898,13 +7566,13 @@
       <c r="H64" s="7">
         <v>0</v>
       </c>
-      <c r="I64" s="55">
-        <v>0</v>
-      </c>
-      <c r="J64" s="57">
+      <c r="I64" s="46">
+        <v>0</v>
+      </c>
+      <c r="J64" s="48">
         <v>124</v>
       </c>
-      <c r="K64" s="42"/>
+      <c r="K64" s="6"/>
       <c r="L64" s="16">
         <v>60</v>
       </c>
@@ -5914,11 +7582,11 @@
       </c>
     </row>
     <row r="65" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B65" s="48">
+      <c r="B65" s="42">
         <f t="shared" si="2"/>
         <v>61</v>
       </c>
-      <c r="C65" s="40">
+      <c r="C65" s="37">
         <v>0</v>
       </c>
       <c r="D65" s="7">
@@ -5936,13 +7604,13 @@
       <c r="H65" s="7">
         <v>0</v>
       </c>
-      <c r="I65" s="55">
-        <v>1</v>
-      </c>
-      <c r="J65" s="57">
+      <c r="I65" s="46">
+        <v>1</v>
+      </c>
+      <c r="J65" s="48">
         <v>125</v>
       </c>
-      <c r="K65" s="42"/>
+      <c r="K65" s="6"/>
       <c r="L65" s="16">
         <v>61</v>
       </c>
@@ -5952,11 +7620,11 @@
       </c>
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B66" s="48">
+      <c r="B66" s="42">
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="C66" s="40">
+      <c r="C66" s="37">
         <v>0</v>
       </c>
       <c r="D66" s="7">
@@ -5974,13 +7642,13 @@
       <c r="H66" s="7">
         <v>1</v>
       </c>
-      <c r="I66" s="55">
-        <v>0</v>
-      </c>
-      <c r="J66" s="57">
+      <c r="I66" s="46">
+        <v>0</v>
+      </c>
+      <c r="J66" s="48">
         <v>126</v>
       </c>
-      <c r="K66" s="42"/>
+      <c r="K66" s="6"/>
       <c r="L66" s="16">
         <v>62</v>
       </c>
@@ -5990,11 +7658,11 @@
       </c>
     </row>
     <row r="67" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B67" s="49">
+      <c r="B67" s="43">
         <f t="shared" si="2"/>
         <v>63</v>
       </c>
-      <c r="C67" s="38">
+      <c r="C67" s="35">
         <v>0</v>
       </c>
       <c r="D67" s="12">
@@ -6012,13 +7680,13 @@
       <c r="H67" s="12">
         <v>1</v>
       </c>
-      <c r="I67" s="56">
-        <v>1</v>
-      </c>
-      <c r="J67" s="58">
+      <c r="I67" s="47">
+        <v>1</v>
+      </c>
+      <c r="J67" s="49">
         <v>127</v>
       </c>
-      <c r="K67" s="42"/>
+      <c r="K67" s="6"/>
       <c r="L67" s="26">
         <v>63</v>
       </c>
@@ -6028,11 +7696,11 @@
       </c>
     </row>
     <row r="68" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B68" s="50">
+      <c r="B68" s="44">
         <f t="shared" si="2"/>
         <v>64</v>
       </c>
-      <c r="C68" s="39">
+      <c r="C68" s="36">
         <v>1</v>
       </c>
       <c r="D68" s="28">
@@ -6050,13 +7718,13 @@
       <c r="H68" s="28">
         <v>0</v>
       </c>
-      <c r="I68" s="54">
-        <v>0</v>
-      </c>
-      <c r="J68" s="59">
-        <v>0</v>
-      </c>
-      <c r="K68" s="42"/>
+      <c r="I68" s="45">
+        <v>0</v>
+      </c>
+      <c r="J68" s="50">
+        <v>0</v>
+      </c>
+      <c r="K68" s="6"/>
       <c r="L68" s="18">
         <v>64</v>
       </c>
@@ -6066,11 +7734,11 @@
       </c>
     </row>
     <row r="69" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B69" s="48">
+      <c r="B69" s="42">
         <f t="shared" si="2"/>
         <v>65</v>
       </c>
-      <c r="C69" s="40">
+      <c r="C69" s="37">
         <v>1</v>
       </c>
       <c r="D69" s="7">
@@ -6088,13 +7756,13 @@
       <c r="H69" s="7">
         <v>0</v>
       </c>
-      <c r="I69" s="55">
-        <v>1</v>
-      </c>
-      <c r="J69" s="57">
-        <v>1</v>
-      </c>
-      <c r="K69" s="42"/>
+      <c r="I69" s="46">
+        <v>1</v>
+      </c>
+      <c r="J69" s="48">
+        <v>1</v>
+      </c>
+      <c r="K69" s="6"/>
       <c r="L69" s="20">
         <v>65</v>
       </c>
@@ -6104,11 +7772,11 @@
       </c>
     </row>
     <row r="70" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B70" s="48">
+      <c r="B70" s="42">
         <f t="shared" si="2"/>
         <v>66</v>
       </c>
-      <c r="C70" s="40">
+      <c r="C70" s="37">
         <v>1</v>
       </c>
       <c r="D70" s="7">
@@ -6126,13 +7794,13 @@
       <c r="H70" s="7">
         <v>1</v>
       </c>
-      <c r="I70" s="55">
-        <v>0</v>
-      </c>
-      <c r="J70" s="57">
+      <c r="I70" s="46">
+        <v>0</v>
+      </c>
+      <c r="J70" s="48">
         <v>2</v>
       </c>
-      <c r="K70" s="42"/>
+      <c r="K70" s="6"/>
       <c r="L70" s="20">
         <v>66</v>
       </c>
@@ -6142,11 +7810,11 @@
       </c>
     </row>
     <row r="71" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B71" s="48">
+      <c r="B71" s="42">
         <f t="shared" si="2"/>
         <v>67</v>
       </c>
-      <c r="C71" s="40">
+      <c r="C71" s="37">
         <v>1</v>
       </c>
       <c r="D71" s="7">
@@ -6164,13 +7832,13 @@
       <c r="H71" s="7">
         <v>1</v>
       </c>
-      <c r="I71" s="55">
-        <v>1</v>
-      </c>
-      <c r="J71" s="57">
+      <c r="I71" s="46">
+        <v>1</v>
+      </c>
+      <c r="J71" s="48">
         <v>3</v>
       </c>
-      <c r="K71" s="42"/>
+      <c r="K71" s="6"/>
       <c r="L71" s="20">
         <v>67</v>
       </c>
@@ -6180,11 +7848,11 @@
       </c>
     </row>
     <row r="72" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B72" s="48">
+      <c r="B72" s="42">
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
-      <c r="C72" s="40">
+      <c r="C72" s="37">
         <v>1</v>
       </c>
       <c r="D72" s="7">
@@ -6202,13 +7870,13 @@
       <c r="H72" s="7">
         <v>0</v>
       </c>
-      <c r="I72" s="55">
-        <v>0</v>
-      </c>
-      <c r="J72" s="57">
+      <c r="I72" s="46">
+        <v>0</v>
+      </c>
+      <c r="J72" s="48">
         <v>4</v>
       </c>
-      <c r="K72" s="42"/>
+      <c r="K72" s="6"/>
       <c r="L72" s="20">
         <v>68</v>
       </c>
@@ -6218,11 +7886,11 @@
       </c>
     </row>
     <row r="73" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B73" s="48">
+      <c r="B73" s="42">
         <f t="shared" ref="B73:B131" si="5">BIN2DEC(_xlfn.CONCAT(C73:I73))</f>
         <v>69</v>
       </c>
-      <c r="C73" s="40">
+      <c r="C73" s="37">
         <v>1</v>
       </c>
       <c r="D73" s="7">
@@ -6240,15 +7908,15 @@
       <c r="H73" s="7">
         <v>0</v>
       </c>
-      <c r="I73" s="55">
-        <v>1</v>
-      </c>
-      <c r="J73" s="57">
+      <c r="I73" s="46">
+        <v>1</v>
+      </c>
+      <c r="J73" s="48">
         <v>5</v>
       </c>
-      <c r="K73" s="42"/>
+      <c r="K73" s="6"/>
       <c r="L73" s="20">
-        <f t="shared" ref="L69:L131" si="6">J73</f>
+        <f t="shared" ref="L73:L126" si="6">J73</f>
         <v>5</v>
       </c>
       <c r="M73" s="21">
@@ -6257,11 +7925,11 @@
       </c>
     </row>
     <row r="74" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B74" s="48">
+      <c r="B74" s="42">
         <f t="shared" si="5"/>
         <v>70</v>
       </c>
-      <c r="C74" s="40">
+      <c r="C74" s="37">
         <v>1</v>
       </c>
       <c r="D74" s="7">
@@ -6279,13 +7947,13 @@
       <c r="H74" s="7">
         <v>1</v>
       </c>
-      <c r="I74" s="55">
-        <v>0</v>
-      </c>
-      <c r="J74" s="57">
+      <c r="I74" s="46">
+        <v>0</v>
+      </c>
+      <c r="J74" s="48">
         <v>6</v>
       </c>
-      <c r="K74" s="42"/>
+      <c r="K74" s="6"/>
       <c r="L74" s="20">
         <f t="shared" si="6"/>
         <v>6</v>
@@ -6296,11 +7964,11 @@
       </c>
     </row>
     <row r="75" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B75" s="48">
+      <c r="B75" s="42">
         <f t="shared" si="5"/>
         <v>71</v>
       </c>
-      <c r="C75" s="40">
+      <c r="C75" s="37">
         <v>1</v>
       </c>
       <c r="D75" s="7">
@@ -6318,13 +7986,13 @@
       <c r="H75" s="7">
         <v>1</v>
       </c>
-      <c r="I75" s="55">
-        <v>1</v>
-      </c>
-      <c r="J75" s="57">
+      <c r="I75" s="46">
+        <v>1</v>
+      </c>
+      <c r="J75" s="48">
         <v>7</v>
       </c>
-      <c r="K75" s="42"/>
+      <c r="K75" s="6"/>
       <c r="L75" s="20">
         <f t="shared" si="6"/>
         <v>7</v>
@@ -6335,11 +8003,11 @@
       </c>
     </row>
     <row r="76" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B76" s="48">
+      <c r="B76" s="42">
         <f t="shared" si="5"/>
         <v>72</v>
       </c>
-      <c r="C76" s="40">
+      <c r="C76" s="37">
         <v>1</v>
       </c>
       <c r="D76" s="7">
@@ -6357,13 +8025,13 @@
       <c r="H76" s="7">
         <v>0</v>
       </c>
-      <c r="I76" s="55">
-        <v>0</v>
-      </c>
-      <c r="J76" s="57">
+      <c r="I76" s="46">
+        <v>0</v>
+      </c>
+      <c r="J76" s="48">
         <v>8</v>
       </c>
-      <c r="K76" s="42"/>
+      <c r="K76" s="6"/>
       <c r="L76" s="20">
         <f t="shared" si="6"/>
         <v>8</v>
@@ -6374,11 +8042,11 @@
       </c>
     </row>
     <row r="77" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B77" s="48">
+      <c r="B77" s="42">
         <f t="shared" si="5"/>
         <v>73</v>
       </c>
-      <c r="C77" s="40">
+      <c r="C77" s="37">
         <v>1</v>
       </c>
       <c r="D77" s="7">
@@ -6396,13 +8064,13 @@
       <c r="H77" s="7">
         <v>0</v>
       </c>
-      <c r="I77" s="55">
-        <v>1</v>
-      </c>
-      <c r="J77" s="57">
+      <c r="I77" s="46">
+        <v>1</v>
+      </c>
+      <c r="J77" s="48">
         <v>9</v>
       </c>
-      <c r="K77" s="42"/>
+      <c r="K77" s="6"/>
       <c r="L77" s="20">
         <f t="shared" si="6"/>
         <v>9</v>
@@ -6413,11 +8081,11 @@
       </c>
     </row>
     <row r="78" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B78" s="48">
+      <c r="B78" s="42">
         <f t="shared" si="5"/>
         <v>74</v>
       </c>
-      <c r="C78" s="40">
+      <c r="C78" s="37">
         <v>1</v>
       </c>
       <c r="D78" s="7">
@@ -6435,13 +8103,13 @@
       <c r="H78" s="7">
         <v>1</v>
       </c>
-      <c r="I78" s="55">
-        <v>0</v>
-      </c>
-      <c r="J78" s="57">
+      <c r="I78" s="46">
+        <v>0</v>
+      </c>
+      <c r="J78" s="48">
         <v>10</v>
       </c>
-      <c r="K78" s="42"/>
+      <c r="K78" s="6"/>
       <c r="L78" s="20">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -6452,11 +8120,11 @@
       </c>
     </row>
     <row r="79" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B79" s="48">
+      <c r="B79" s="42">
         <f t="shared" si="5"/>
         <v>75</v>
       </c>
-      <c r="C79" s="40">
+      <c r="C79" s="37">
         <v>1</v>
       </c>
       <c r="D79" s="7">
@@ -6474,13 +8142,13 @@
       <c r="H79" s="7">
         <v>1</v>
       </c>
-      <c r="I79" s="55">
-        <v>1</v>
-      </c>
-      <c r="J79" s="57">
+      <c r="I79" s="46">
+        <v>1</v>
+      </c>
+      <c r="J79" s="48">
         <v>11</v>
       </c>
-      <c r="K79" s="42"/>
+      <c r="K79" s="6"/>
       <c r="L79" s="20">
         <f t="shared" si="6"/>
         <v>11</v>
@@ -6491,11 +8159,11 @@
       </c>
     </row>
     <row r="80" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B80" s="48">
+      <c r="B80" s="42">
         <f t="shared" si="5"/>
         <v>76</v>
       </c>
-      <c r="C80" s="40">
+      <c r="C80" s="37">
         <v>1</v>
       </c>
       <c r="D80" s="7">
@@ -6513,13 +8181,13 @@
       <c r="H80" s="7">
         <v>0</v>
       </c>
-      <c r="I80" s="55">
-        <v>0</v>
-      </c>
-      <c r="J80" s="57">
+      <c r="I80" s="46">
+        <v>0</v>
+      </c>
+      <c r="J80" s="48">
         <v>12</v>
       </c>
-      <c r="K80" s="42"/>
+      <c r="K80" s="6"/>
       <c r="L80" s="20">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -6530,11 +8198,11 @@
       </c>
     </row>
     <row r="81" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B81" s="48">
+      <c r="B81" s="42">
         <f t="shared" si="5"/>
         <v>77</v>
       </c>
-      <c r="C81" s="40">
+      <c r="C81" s="37">
         <v>1</v>
       </c>
       <c r="D81" s="7">
@@ -6552,13 +8220,13 @@
       <c r="H81" s="7">
         <v>0</v>
       </c>
-      <c r="I81" s="55">
-        <v>1</v>
-      </c>
-      <c r="J81" s="57">
+      <c r="I81" s="46">
+        <v>1</v>
+      </c>
+      <c r="J81" s="48">
         <v>13</v>
       </c>
-      <c r="K81" s="42"/>
+      <c r="K81" s="6"/>
       <c r="L81" s="20">
         <f t="shared" si="6"/>
         <v>13</v>
@@ -6569,11 +8237,11 @@
       </c>
     </row>
     <row r="82" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B82" s="48">
+      <c r="B82" s="42">
         <f t="shared" si="5"/>
         <v>78</v>
       </c>
-      <c r="C82" s="40">
+      <c r="C82" s="37">
         <v>1</v>
       </c>
       <c r="D82" s="7">
@@ -6591,13 +8259,13 @@
       <c r="H82" s="7">
         <v>1</v>
       </c>
-      <c r="I82" s="55">
-        <v>0</v>
-      </c>
-      <c r="J82" s="57">
+      <c r="I82" s="46">
+        <v>0</v>
+      </c>
+      <c r="J82" s="48">
         <v>14</v>
       </c>
-      <c r="K82" s="42"/>
+      <c r="K82" s="6"/>
       <c r="L82" s="20">
         <f t="shared" si="6"/>
         <v>14</v>
@@ -6608,11 +8276,11 @@
       </c>
     </row>
     <row r="83" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B83" s="48">
+      <c r="B83" s="42">
         <f t="shared" si="5"/>
         <v>79</v>
       </c>
-      <c r="C83" s="40">
+      <c r="C83" s="37">
         <v>1</v>
       </c>
       <c r="D83" s="7">
@@ -6630,13 +8298,13 @@
       <c r="H83" s="7">
         <v>1</v>
       </c>
-      <c r="I83" s="55">
-        <v>1</v>
-      </c>
-      <c r="J83" s="57">
+      <c r="I83" s="46">
+        <v>1</v>
+      </c>
+      <c r="J83" s="48">
         <v>15</v>
       </c>
-      <c r="K83" s="42"/>
+      <c r="K83" s="6"/>
       <c r="L83" s="20">
         <f t="shared" si="6"/>
         <v>15</v>
@@ -6647,11 +8315,11 @@
       </c>
     </row>
     <row r="84" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B84" s="48">
+      <c r="B84" s="42">
         <f t="shared" si="5"/>
         <v>80</v>
       </c>
-      <c r="C84" s="40">
+      <c r="C84" s="37">
         <v>1</v>
       </c>
       <c r="D84" s="7">
@@ -6669,13 +8337,13 @@
       <c r="H84" s="7">
         <v>0</v>
       </c>
-      <c r="I84" s="55">
-        <v>0</v>
-      </c>
-      <c r="J84" s="57">
+      <c r="I84" s="46">
+        <v>0</v>
+      </c>
+      <c r="J84" s="48">
         <v>16</v>
       </c>
-      <c r="K84" s="42"/>
+      <c r="K84" s="6"/>
       <c r="L84" s="20">
         <f t="shared" si="6"/>
         <v>16</v>
@@ -6686,11 +8354,11 @@
       </c>
     </row>
     <row r="85" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B85" s="48">
+      <c r="B85" s="42">
         <f t="shared" si="5"/>
         <v>81</v>
       </c>
-      <c r="C85" s="40">
+      <c r="C85" s="37">
         <v>1</v>
       </c>
       <c r="D85" s="7">
@@ -6708,13 +8376,13 @@
       <c r="H85" s="7">
         <v>0</v>
       </c>
-      <c r="I85" s="55">
-        <v>1</v>
-      </c>
-      <c r="J85" s="57">
-        <v>17</v>
-      </c>
-      <c r="K85" s="42"/>
+      <c r="I85" s="46">
+        <v>1</v>
+      </c>
+      <c r="J85" s="48">
+        <v>17</v>
+      </c>
+      <c r="K85" s="6"/>
       <c r="L85" s="20">
         <f t="shared" si="6"/>
         <v>17</v>
@@ -6725,11 +8393,11 @@
       </c>
     </row>
     <row r="86" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B86" s="48">
+      <c r="B86" s="42">
         <f t="shared" si="5"/>
         <v>82</v>
       </c>
-      <c r="C86" s="40">
+      <c r="C86" s="37">
         <v>1</v>
       </c>
       <c r="D86" s="7">
@@ -6747,13 +8415,13 @@
       <c r="H86" s="7">
         <v>1</v>
       </c>
-      <c r="I86" s="55">
-        <v>0</v>
-      </c>
-      <c r="J86" s="57">
+      <c r="I86" s="46">
+        <v>0</v>
+      </c>
+      <c r="J86" s="48">
         <v>18</v>
       </c>
-      <c r="K86" s="42"/>
+      <c r="K86" s="6"/>
       <c r="L86" s="20">
         <f t="shared" si="6"/>
         <v>18</v>
@@ -6764,11 +8432,11 @@
       </c>
     </row>
     <row r="87" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B87" s="48">
+      <c r="B87" s="42">
         <f t="shared" si="5"/>
         <v>83</v>
       </c>
-      <c r="C87" s="40">
+      <c r="C87" s="37">
         <v>1</v>
       </c>
       <c r="D87" s="7">
@@ -6786,13 +8454,13 @@
       <c r="H87" s="7">
         <v>1</v>
       </c>
-      <c r="I87" s="55">
-        <v>1</v>
-      </c>
-      <c r="J87" s="57">
+      <c r="I87" s="46">
+        <v>1</v>
+      </c>
+      <c r="J87" s="48">
         <v>19</v>
       </c>
-      <c r="K87" s="42"/>
+      <c r="K87" s="6"/>
       <c r="L87" s="20">
         <f t="shared" si="6"/>
         <v>19</v>
@@ -6803,11 +8471,11 @@
       </c>
     </row>
     <row r="88" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B88" s="48">
+      <c r="B88" s="42">
         <f t="shared" si="5"/>
         <v>84</v>
       </c>
-      <c r="C88" s="40">
+      <c r="C88" s="37">
         <v>1</v>
       </c>
       <c r="D88" s="7">
@@ -6825,13 +8493,13 @@
       <c r="H88" s="7">
         <v>0</v>
       </c>
-      <c r="I88" s="55">
-        <v>0</v>
-      </c>
-      <c r="J88" s="57">
+      <c r="I88" s="46">
+        <v>0</v>
+      </c>
+      <c r="J88" s="48">
         <v>20</v>
       </c>
-      <c r="K88" s="42"/>
+      <c r="K88" s="6"/>
       <c r="L88" s="20">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -6842,11 +8510,11 @@
       </c>
     </row>
     <row r="89" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B89" s="48">
+      <c r="B89" s="42">
         <f t="shared" si="5"/>
         <v>85</v>
       </c>
-      <c r="C89" s="40">
+      <c r="C89" s="37">
         <v>1</v>
       </c>
       <c r="D89" s="7">
@@ -6864,13 +8532,13 @@
       <c r="H89" s="7">
         <v>0</v>
       </c>
-      <c r="I89" s="55">
-        <v>1</v>
-      </c>
-      <c r="J89" s="57">
+      <c r="I89" s="46">
+        <v>1</v>
+      </c>
+      <c r="J89" s="48">
         <v>21</v>
       </c>
-      <c r="K89" s="42"/>
+      <c r="K89" s="6"/>
       <c r="L89" s="20">
         <f t="shared" si="6"/>
         <v>21</v>
@@ -6881,11 +8549,11 @@
       </c>
     </row>
     <row r="90" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B90" s="48">
+      <c r="B90" s="42">
         <f t="shared" si="5"/>
         <v>86</v>
       </c>
-      <c r="C90" s="40">
+      <c r="C90" s="37">
         <v>1</v>
       </c>
       <c r="D90" s="7">
@@ -6903,13 +8571,13 @@
       <c r="H90" s="7">
         <v>1</v>
       </c>
-      <c r="I90" s="55">
-        <v>0</v>
-      </c>
-      <c r="J90" s="57">
+      <c r="I90" s="46">
+        <v>0</v>
+      </c>
+      <c r="J90" s="48">
         <v>22</v>
       </c>
-      <c r="K90" s="42"/>
+      <c r="K90" s="6"/>
       <c r="L90" s="20">
         <f t="shared" si="6"/>
         <v>22</v>
@@ -6920,11 +8588,11 @@
       </c>
     </row>
     <row r="91" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B91" s="48">
+      <c r="B91" s="42">
         <f t="shared" si="5"/>
         <v>87</v>
       </c>
-      <c r="C91" s="40">
+      <c r="C91" s="37">
         <v>1</v>
       </c>
       <c r="D91" s="7">
@@ -6942,13 +8610,13 @@
       <c r="H91" s="7">
         <v>1</v>
       </c>
-      <c r="I91" s="55">
-        <v>1</v>
-      </c>
-      <c r="J91" s="57">
+      <c r="I91" s="46">
+        <v>1</v>
+      </c>
+      <c r="J91" s="48">
         <v>23</v>
       </c>
-      <c r="K91" s="42"/>
+      <c r="K91" s="6"/>
       <c r="L91" s="20">
         <f t="shared" si="6"/>
         <v>23</v>
@@ -6959,11 +8627,11 @@
       </c>
     </row>
     <row r="92" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B92" s="48">
+      <c r="B92" s="42">
         <f t="shared" si="5"/>
         <v>88</v>
       </c>
-      <c r="C92" s="40">
+      <c r="C92" s="37">
         <v>1</v>
       </c>
       <c r="D92" s="7">
@@ -6981,13 +8649,13 @@
       <c r="H92" s="7">
         <v>0</v>
       </c>
-      <c r="I92" s="55">
-        <v>0</v>
-      </c>
-      <c r="J92" s="57">
+      <c r="I92" s="46">
+        <v>0</v>
+      </c>
+      <c r="J92" s="48">
         <v>24</v>
       </c>
-      <c r="K92" s="42"/>
+      <c r="K92" s="6"/>
       <c r="L92" s="20">
         <f t="shared" si="6"/>
         <v>24</v>
@@ -6998,11 +8666,11 @@
       </c>
     </row>
     <row r="93" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B93" s="48">
+      <c r="B93" s="42">
         <f t="shared" si="5"/>
         <v>89</v>
       </c>
-      <c r="C93" s="40">
+      <c r="C93" s="37">
         <v>1</v>
       </c>
       <c r="D93" s="7">
@@ -7020,13 +8688,13 @@
       <c r="H93" s="7">
         <v>0</v>
       </c>
-      <c r="I93" s="55">
-        <v>1</v>
-      </c>
-      <c r="J93" s="57">
+      <c r="I93" s="46">
+        <v>1</v>
+      </c>
+      <c r="J93" s="48">
         <v>25</v>
       </c>
-      <c r="K93" s="42"/>
+      <c r="K93" s="6"/>
       <c r="L93" s="20">
         <f t="shared" si="6"/>
         <v>25</v>
@@ -7037,11 +8705,11 @@
       </c>
     </row>
     <row r="94" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B94" s="48">
+      <c r="B94" s="42">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="C94" s="40">
+      <c r="C94" s="37">
         <v>1</v>
       </c>
       <c r="D94" s="7">
@@ -7059,13 +8727,13 @@
       <c r="H94" s="7">
         <v>1</v>
       </c>
-      <c r="I94" s="55">
-        <v>0</v>
-      </c>
-      <c r="J94" s="57">
+      <c r="I94" s="46">
+        <v>0</v>
+      </c>
+      <c r="J94" s="48">
         <v>26</v>
       </c>
-      <c r="K94" s="42"/>
+      <c r="K94" s="6"/>
       <c r="L94" s="20">
         <f t="shared" si="6"/>
         <v>26</v>
@@ -7076,11 +8744,11 @@
       </c>
     </row>
     <row r="95" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B95" s="48">
+      <c r="B95" s="42">
         <f t="shared" si="5"/>
         <v>91</v>
       </c>
-      <c r="C95" s="40">
+      <c r="C95" s="37">
         <v>1</v>
       </c>
       <c r="D95" s="7">
@@ -7098,13 +8766,13 @@
       <c r="H95" s="7">
         <v>1</v>
       </c>
-      <c r="I95" s="55">
-        <v>1</v>
-      </c>
-      <c r="J95" s="57">
+      <c r="I95" s="46">
+        <v>1</v>
+      </c>
+      <c r="J95" s="48">
         <v>27</v>
       </c>
-      <c r="K95" s="42"/>
+      <c r="K95" s="6"/>
       <c r="L95" s="20">
         <f t="shared" si="6"/>
         <v>27</v>
@@ -7115,11 +8783,11 @@
       </c>
     </row>
     <row r="96" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B96" s="48">
+      <c r="B96" s="42">
         <f t="shared" si="5"/>
         <v>92</v>
       </c>
-      <c r="C96" s="40">
+      <c r="C96" s="37">
         <v>1</v>
       </c>
       <c r="D96" s="7">
@@ -7137,13 +8805,13 @@
       <c r="H96" s="7">
         <v>0</v>
       </c>
-      <c r="I96" s="55">
-        <v>0</v>
-      </c>
-      <c r="J96" s="57">
+      <c r="I96" s="46">
+        <v>0</v>
+      </c>
+      <c r="J96" s="48">
         <v>28</v>
       </c>
-      <c r="K96" s="42"/>
+      <c r="K96" s="6"/>
       <c r="L96" s="20">
         <f t="shared" si="6"/>
         <v>28</v>
@@ -7154,11 +8822,11 @@
       </c>
     </row>
     <row r="97" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B97" s="48">
+      <c r="B97" s="42">
         <f t="shared" si="5"/>
         <v>93</v>
       </c>
-      <c r="C97" s="40">
+      <c r="C97" s="37">
         <v>1</v>
       </c>
       <c r="D97" s="7">
@@ -7176,13 +8844,13 @@
       <c r="H97" s="7">
         <v>0</v>
       </c>
-      <c r="I97" s="55">
-        <v>1</v>
-      </c>
-      <c r="J97" s="57">
+      <c r="I97" s="46">
+        <v>1</v>
+      </c>
+      <c r="J97" s="48">
         <v>29</v>
       </c>
-      <c r="K97" s="42"/>
+      <c r="K97" s="6"/>
       <c r="L97" s="20">
         <f t="shared" si="6"/>
         <v>29</v>
@@ -7193,11 +8861,11 @@
       </c>
     </row>
     <row r="98" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B98" s="48">
+      <c r="B98" s="42">
         <f t="shared" si="5"/>
         <v>94</v>
       </c>
-      <c r="C98" s="40">
+      <c r="C98" s="37">
         <v>1</v>
       </c>
       <c r="D98" s="7">
@@ -7215,13 +8883,13 @@
       <c r="H98" s="7">
         <v>1</v>
       </c>
-      <c r="I98" s="55">
-        <v>0</v>
-      </c>
-      <c r="J98" s="57">
+      <c r="I98" s="46">
+        <v>0</v>
+      </c>
+      <c r="J98" s="48">
         <v>30</v>
       </c>
-      <c r="K98" s="42"/>
+      <c r="K98" s="6"/>
       <c r="L98" s="20">
         <f t="shared" si="6"/>
         <v>30</v>
@@ -7232,11 +8900,11 @@
       </c>
     </row>
     <row r="99" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B99" s="48">
+      <c r="B99" s="42">
         <f t="shared" si="5"/>
         <v>95</v>
       </c>
-      <c r="C99" s="40">
+      <c r="C99" s="37">
         <v>1</v>
       </c>
       <c r="D99" s="7">
@@ -7254,13 +8922,13 @@
       <c r="H99" s="7">
         <v>1</v>
       </c>
-      <c r="I99" s="55">
-        <v>1</v>
-      </c>
-      <c r="J99" s="57">
+      <c r="I99" s="46">
+        <v>1</v>
+      </c>
+      <c r="J99" s="48">
         <v>31</v>
       </c>
-      <c r="K99" s="42"/>
+      <c r="K99" s="6"/>
       <c r="L99" s="20">
         <f t="shared" si="6"/>
         <v>31</v>
@@ -7271,11 +8939,11 @@
       </c>
     </row>
     <row r="100" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B100" s="48">
+      <c r="B100" s="42">
         <f t="shared" si="5"/>
         <v>96</v>
       </c>
-      <c r="C100" s="40">
+      <c r="C100" s="37">
         <v>1</v>
       </c>
       <c r="D100" s="7">
@@ -7293,13 +8961,13 @@
       <c r="H100" s="7">
         <v>0</v>
       </c>
-      <c r="I100" s="55">
-        <v>0</v>
-      </c>
-      <c r="J100" s="57">
+      <c r="I100" s="46">
+        <v>0</v>
+      </c>
+      <c r="J100" s="48">
         <v>32</v>
       </c>
-      <c r="K100" s="42"/>
+      <c r="K100" s="6"/>
       <c r="L100" s="20">
         <f t="shared" si="6"/>
         <v>32</v>
@@ -7310,11 +8978,11 @@
       </c>
     </row>
     <row r="101" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B101" s="48">
+      <c r="B101" s="42">
         <f t="shared" si="5"/>
         <v>97</v>
       </c>
-      <c r="C101" s="40">
+      <c r="C101" s="37">
         <v>1</v>
       </c>
       <c r="D101" s="7">
@@ -7332,13 +9000,13 @@
       <c r="H101" s="7">
         <v>0</v>
       </c>
-      <c r="I101" s="55">
-        <v>1</v>
-      </c>
-      <c r="J101" s="57">
+      <c r="I101" s="46">
+        <v>1</v>
+      </c>
+      <c r="J101" s="48">
         <v>33</v>
       </c>
-      <c r="K101" s="42"/>
+      <c r="K101" s="6"/>
       <c r="L101" s="20">
         <f t="shared" si="6"/>
         <v>33</v>
@@ -7349,11 +9017,11 @@
       </c>
     </row>
     <row r="102" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B102" s="48">
+      <c r="B102" s="42">
         <f t="shared" si="5"/>
         <v>98</v>
       </c>
-      <c r="C102" s="40">
+      <c r="C102" s="37">
         <v>1</v>
       </c>
       <c r="D102" s="7">
@@ -7371,13 +9039,13 @@
       <c r="H102" s="7">
         <v>1</v>
       </c>
-      <c r="I102" s="55">
-        <v>0</v>
-      </c>
-      <c r="J102" s="57">
+      <c r="I102" s="46">
+        <v>0</v>
+      </c>
+      <c r="J102" s="48">
         <v>34</v>
       </c>
-      <c r="K102" s="42"/>
+      <c r="K102" s="6"/>
       <c r="L102" s="20">
         <f t="shared" si="6"/>
         <v>34</v>
@@ -7388,11 +9056,11 @@
       </c>
     </row>
     <row r="103" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B103" s="48">
+      <c r="B103" s="42">
         <f t="shared" si="5"/>
         <v>99</v>
       </c>
-      <c r="C103" s="40">
+      <c r="C103" s="37">
         <v>1</v>
       </c>
       <c r="D103" s="7">
@@ -7410,13 +9078,13 @@
       <c r="H103" s="7">
         <v>1</v>
       </c>
-      <c r="I103" s="55">
-        <v>1</v>
-      </c>
-      <c r="J103" s="57">
+      <c r="I103" s="46">
+        <v>1</v>
+      </c>
+      <c r="J103" s="48">
         <v>35</v>
       </c>
-      <c r="K103" s="42"/>
+      <c r="K103" s="6"/>
       <c r="L103" s="20">
         <f t="shared" si="6"/>
         <v>35</v>
@@ -7427,11 +9095,11 @@
       </c>
     </row>
     <row r="104" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B104" s="48">
+      <c r="B104" s="42">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="C104" s="40">
+      <c r="C104" s="37">
         <v>1</v>
       </c>
       <c r="D104" s="7">
@@ -7449,13 +9117,13 @@
       <c r="H104" s="7">
         <v>0</v>
       </c>
-      <c r="I104" s="55">
-        <v>0</v>
-      </c>
-      <c r="J104" s="57">
+      <c r="I104" s="46">
+        <v>0</v>
+      </c>
+      <c r="J104" s="48">
         <v>36</v>
       </c>
-      <c r="K104" s="42"/>
+      <c r="K104" s="6"/>
       <c r="L104" s="20">
         <f t="shared" si="6"/>
         <v>36</v>
@@ -7466,11 +9134,11 @@
       </c>
     </row>
     <row r="105" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B105" s="48">
+      <c r="B105" s="42">
         <f t="shared" si="5"/>
         <v>101</v>
       </c>
-      <c r="C105" s="40">
+      <c r="C105" s="37">
         <v>1</v>
       </c>
       <c r="D105" s="7">
@@ -7488,13 +9156,13 @@
       <c r="H105" s="7">
         <v>0</v>
       </c>
-      <c r="I105" s="55">
-        <v>1</v>
-      </c>
-      <c r="J105" s="57">
+      <c r="I105" s="46">
+        <v>1</v>
+      </c>
+      <c r="J105" s="48">
         <v>37</v>
       </c>
-      <c r="K105" s="42"/>
+      <c r="K105" s="6"/>
       <c r="L105" s="20">
         <f t="shared" si="6"/>
         <v>37</v>
@@ -7505,11 +9173,11 @@
       </c>
     </row>
     <row r="106" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B106" s="48">
+      <c r="B106" s="42">
         <f t="shared" si="5"/>
         <v>102</v>
       </c>
-      <c r="C106" s="40">
+      <c r="C106" s="37">
         <v>1</v>
       </c>
       <c r="D106" s="7">
@@ -7527,13 +9195,13 @@
       <c r="H106" s="7">
         <v>1</v>
       </c>
-      <c r="I106" s="55">
-        <v>0</v>
-      </c>
-      <c r="J106" s="57">
+      <c r="I106" s="46">
+        <v>0</v>
+      </c>
+      <c r="J106" s="48">
         <v>38</v>
       </c>
-      <c r="K106" s="42"/>
+      <c r="K106" s="6"/>
       <c r="L106" s="20">
         <f t="shared" si="6"/>
         <v>38</v>
@@ -7544,11 +9212,11 @@
       </c>
     </row>
     <row r="107" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B107" s="48">
+      <c r="B107" s="42">
         <f t="shared" si="5"/>
         <v>103</v>
       </c>
-      <c r="C107" s="40">
+      <c r="C107" s="37">
         <v>1</v>
       </c>
       <c r="D107" s="7">
@@ -7566,13 +9234,13 @@
       <c r="H107" s="7">
         <v>1</v>
       </c>
-      <c r="I107" s="55">
-        <v>1</v>
-      </c>
-      <c r="J107" s="57">
+      <c r="I107" s="46">
+        <v>1</v>
+      </c>
+      <c r="J107" s="48">
         <v>39</v>
       </c>
-      <c r="K107" s="42"/>
+      <c r="K107" s="6"/>
       <c r="L107" s="20">
         <f t="shared" si="6"/>
         <v>39</v>
@@ -7583,11 +9251,11 @@
       </c>
     </row>
     <row r="108" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B108" s="48">
+      <c r="B108" s="42">
         <f t="shared" si="5"/>
         <v>104</v>
       </c>
-      <c r="C108" s="40">
+      <c r="C108" s="37">
         <v>1</v>
       </c>
       <c r="D108" s="7">
@@ -7605,13 +9273,13 @@
       <c r="H108" s="7">
         <v>0</v>
       </c>
-      <c r="I108" s="55">
-        <v>0</v>
-      </c>
-      <c r="J108" s="57">
+      <c r="I108" s="46">
+        <v>0</v>
+      </c>
+      <c r="J108" s="48">
         <v>40</v>
       </c>
-      <c r="K108" s="42"/>
+      <c r="K108" s="6"/>
       <c r="L108" s="20">
         <f t="shared" si="6"/>
         <v>40</v>
@@ -7622,11 +9290,11 @@
       </c>
     </row>
     <row r="109" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B109" s="48">
+      <c r="B109" s="42">
         <f t="shared" si="5"/>
         <v>105</v>
       </c>
-      <c r="C109" s="40">
+      <c r="C109" s="37">
         <v>1</v>
       </c>
       <c r="D109" s="7">
@@ -7644,13 +9312,13 @@
       <c r="H109" s="7">
         <v>0</v>
       </c>
-      <c r="I109" s="55">
-        <v>1</v>
-      </c>
-      <c r="J109" s="57">
+      <c r="I109" s="46">
+        <v>1</v>
+      </c>
+      <c r="J109" s="48">
         <v>41</v>
       </c>
-      <c r="K109" s="42"/>
+      <c r="K109" s="6"/>
       <c r="L109" s="20">
         <f t="shared" si="6"/>
         <v>41</v>
@@ -7661,11 +9329,11 @@
       </c>
     </row>
     <row r="110" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B110" s="48">
+      <c r="B110" s="42">
         <f t="shared" si="5"/>
         <v>106</v>
       </c>
-      <c r="C110" s="40">
+      <c r="C110" s="37">
         <v>1</v>
       </c>
       <c r="D110" s="7">
@@ -7683,13 +9351,13 @@
       <c r="H110" s="7">
         <v>1</v>
       </c>
-      <c r="I110" s="55">
-        <v>0</v>
-      </c>
-      <c r="J110" s="57">
+      <c r="I110" s="46">
+        <v>0</v>
+      </c>
+      <c r="J110" s="48">
         <v>42</v>
       </c>
-      <c r="K110" s="42"/>
+      <c r="K110" s="6"/>
       <c r="L110" s="20">
         <f t="shared" si="6"/>
         <v>42</v>
@@ -7700,11 +9368,11 @@
       </c>
     </row>
     <row r="111" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B111" s="48">
+      <c r="B111" s="42">
         <f t="shared" si="5"/>
         <v>107</v>
       </c>
-      <c r="C111" s="40">
+      <c r="C111" s="37">
         <v>1</v>
       </c>
       <c r="D111" s="7">
@@ -7722,13 +9390,13 @@
       <c r="H111" s="7">
         <v>1</v>
       </c>
-      <c r="I111" s="55">
-        <v>1</v>
-      </c>
-      <c r="J111" s="57">
+      <c r="I111" s="46">
+        <v>1</v>
+      </c>
+      <c r="J111" s="48">
         <v>43</v>
       </c>
-      <c r="K111" s="42"/>
+      <c r="K111" s="6"/>
       <c r="L111" s="20">
         <f t="shared" si="6"/>
         <v>43</v>
@@ -7739,11 +9407,11 @@
       </c>
     </row>
     <row r="112" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B112" s="48">
+      <c r="B112" s="42">
         <f t="shared" si="5"/>
         <v>108</v>
       </c>
-      <c r="C112" s="40">
+      <c r="C112" s="37">
         <v>1</v>
       </c>
       <c r="D112" s="7">
@@ -7761,13 +9429,13 @@
       <c r="H112" s="7">
         <v>0</v>
       </c>
-      <c r="I112" s="55">
-        <v>0</v>
-      </c>
-      <c r="J112" s="57">
+      <c r="I112" s="46">
+        <v>0</v>
+      </c>
+      <c r="J112" s="48">
         <v>44</v>
       </c>
-      <c r="K112" s="42"/>
+      <c r="K112" s="6"/>
       <c r="L112" s="20">
         <f t="shared" si="6"/>
         <v>44</v>
@@ -7778,11 +9446,11 @@
       </c>
     </row>
     <row r="113" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B113" s="48">
+      <c r="B113" s="42">
         <f t="shared" si="5"/>
         <v>109</v>
       </c>
-      <c r="C113" s="40">
+      <c r="C113" s="37">
         <v>1</v>
       </c>
       <c r="D113" s="7">
@@ -7800,13 +9468,13 @@
       <c r="H113" s="7">
         <v>0</v>
       </c>
-      <c r="I113" s="55">
-        <v>1</v>
-      </c>
-      <c r="J113" s="57">
+      <c r="I113" s="46">
+        <v>1</v>
+      </c>
+      <c r="J113" s="48">
         <v>45</v>
       </c>
-      <c r="K113" s="42"/>
+      <c r="K113" s="6"/>
       <c r="L113" s="20">
         <f t="shared" si="6"/>
         <v>45</v>
@@ -7817,11 +9485,11 @@
       </c>
     </row>
     <row r="114" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B114" s="48">
+      <c r="B114" s="42">
         <f t="shared" si="5"/>
         <v>110</v>
       </c>
-      <c r="C114" s="40">
+      <c r="C114" s="37">
         <v>1</v>
       </c>
       <c r="D114" s="7">
@@ -7839,13 +9507,13 @@
       <c r="H114" s="7">
         <v>1</v>
       </c>
-      <c r="I114" s="55">
-        <v>0</v>
-      </c>
-      <c r="J114" s="57">
+      <c r="I114" s="46">
+        <v>0</v>
+      </c>
+      <c r="J114" s="48">
         <v>46</v>
       </c>
-      <c r="K114" s="42"/>
+      <c r="K114" s="6"/>
       <c r="L114" s="20">
         <f t="shared" si="6"/>
         <v>46</v>
@@ -7856,11 +9524,11 @@
       </c>
     </row>
     <row r="115" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B115" s="48">
+      <c r="B115" s="42">
         <f t="shared" si="5"/>
         <v>111</v>
       </c>
-      <c r="C115" s="40">
+      <c r="C115" s="37">
         <v>1</v>
       </c>
       <c r="D115" s="7">
@@ -7878,13 +9546,13 @@
       <c r="H115" s="7">
         <v>1</v>
       </c>
-      <c r="I115" s="55">
-        <v>1</v>
-      </c>
-      <c r="J115" s="57">
+      <c r="I115" s="46">
+        <v>1</v>
+      </c>
+      <c r="J115" s="48">
         <v>47</v>
       </c>
-      <c r="K115" s="42"/>
+      <c r="K115" s="6"/>
       <c r="L115" s="20">
         <f t="shared" si="6"/>
         <v>47</v>
@@ -7895,11 +9563,11 @@
       </c>
     </row>
     <row r="116" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B116" s="48">
+      <c r="B116" s="42">
         <f t="shared" si="5"/>
         <v>112</v>
       </c>
-      <c r="C116" s="40">
+      <c r="C116" s="37">
         <v>1</v>
       </c>
       <c r="D116" s="7">
@@ -7917,13 +9585,13 @@
       <c r="H116" s="7">
         <v>0</v>
       </c>
-      <c r="I116" s="55">
-        <v>0</v>
-      </c>
-      <c r="J116" s="57">
+      <c r="I116" s="46">
+        <v>0</v>
+      </c>
+      <c r="J116" s="48">
         <v>48</v>
       </c>
-      <c r="K116" s="42"/>
+      <c r="K116" s="6"/>
       <c r="L116" s="20">
         <f t="shared" si="6"/>
         <v>48</v>
@@ -7934,11 +9602,11 @@
       </c>
     </row>
     <row r="117" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B117" s="48">
+      <c r="B117" s="42">
         <f t="shared" si="5"/>
         <v>113</v>
       </c>
-      <c r="C117" s="40">
+      <c r="C117" s="37">
         <v>1</v>
       </c>
       <c r="D117" s="7">
@@ -7956,13 +9624,13 @@
       <c r="H117" s="7">
         <v>0</v>
       </c>
-      <c r="I117" s="55">
-        <v>1</v>
-      </c>
-      <c r="J117" s="57">
+      <c r="I117" s="46">
+        <v>1</v>
+      </c>
+      <c r="J117" s="48">
         <v>49</v>
       </c>
-      <c r="K117" s="42"/>
+      <c r="K117" s="6"/>
       <c r="L117" s="20">
         <f t="shared" si="6"/>
         <v>49</v>
@@ -7973,11 +9641,11 @@
       </c>
     </row>
     <row r="118" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B118" s="48">
+      <c r="B118" s="42">
         <f t="shared" si="5"/>
         <v>114</v>
       </c>
-      <c r="C118" s="40">
+      <c r="C118" s="37">
         <v>1</v>
       </c>
       <c r="D118" s="7">
@@ -7995,13 +9663,13 @@
       <c r="H118" s="7">
         <v>1</v>
       </c>
-      <c r="I118" s="55">
-        <v>0</v>
-      </c>
-      <c r="J118" s="57">
+      <c r="I118" s="46">
+        <v>0</v>
+      </c>
+      <c r="J118" s="48">
         <v>50</v>
       </c>
-      <c r="K118" s="42"/>
+      <c r="K118" s="6"/>
       <c r="L118" s="20">
         <f t="shared" si="6"/>
         <v>50</v>
@@ -8012,11 +9680,11 @@
       </c>
     </row>
     <row r="119" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B119" s="48">
+      <c r="B119" s="42">
         <f t="shared" si="5"/>
         <v>115</v>
       </c>
-      <c r="C119" s="40">
+      <c r="C119" s="37">
         <v>1</v>
       </c>
       <c r="D119" s="7">
@@ -8034,13 +9702,13 @@
       <c r="H119" s="7">
         <v>1</v>
       </c>
-      <c r="I119" s="55">
-        <v>1</v>
-      </c>
-      <c r="J119" s="57">
+      <c r="I119" s="46">
+        <v>1</v>
+      </c>
+      <c r="J119" s="48">
         <v>51</v>
       </c>
-      <c r="K119" s="42"/>
+      <c r="K119" s="6"/>
       <c r="L119" s="20">
         <f t="shared" si="6"/>
         <v>51</v>
@@ -8051,11 +9719,11 @@
       </c>
     </row>
     <row r="120" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B120" s="48">
+      <c r="B120" s="42">
         <f t="shared" si="5"/>
         <v>116</v>
       </c>
-      <c r="C120" s="40">
+      <c r="C120" s="37">
         <v>1</v>
       </c>
       <c r="D120" s="7">
@@ -8073,13 +9741,13 @@
       <c r="H120" s="7">
         <v>0</v>
       </c>
-      <c r="I120" s="55">
-        <v>0</v>
-      </c>
-      <c r="J120" s="57">
+      <c r="I120" s="46">
+        <v>0</v>
+      </c>
+      <c r="J120" s="48">
         <v>52</v>
       </c>
-      <c r="K120" s="42"/>
+      <c r="K120" s="6"/>
       <c r="L120" s="20">
         <f t="shared" si="6"/>
         <v>52</v>
@@ -8090,11 +9758,11 @@
       </c>
     </row>
     <row r="121" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B121" s="48">
+      <c r="B121" s="42">
         <f t="shared" si="5"/>
         <v>117</v>
       </c>
-      <c r="C121" s="40">
+      <c r="C121" s="37">
         <v>1</v>
       </c>
       <c r="D121" s="7">
@@ -8112,13 +9780,13 @@
       <c r="H121" s="7">
         <v>0</v>
       </c>
-      <c r="I121" s="55">
-        <v>1</v>
-      </c>
-      <c r="J121" s="57">
+      <c r="I121" s="46">
+        <v>1</v>
+      </c>
+      <c r="J121" s="48">
         <v>53</v>
       </c>
-      <c r="K121" s="42"/>
+      <c r="K121" s="6"/>
       <c r="L121" s="20">
         <f t="shared" si="6"/>
         <v>53</v>
@@ -8129,11 +9797,11 @@
       </c>
     </row>
     <row r="122" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B122" s="48">
+      <c r="B122" s="42">
         <f t="shared" si="5"/>
         <v>118</v>
       </c>
-      <c r="C122" s="40">
+      <c r="C122" s="37">
         <v>1</v>
       </c>
       <c r="D122" s="7">
@@ -8151,13 +9819,13 @@
       <c r="H122" s="7">
         <v>1</v>
       </c>
-      <c r="I122" s="55">
-        <v>0</v>
-      </c>
-      <c r="J122" s="57">
+      <c r="I122" s="46">
+        <v>0</v>
+      </c>
+      <c r="J122" s="48">
         <v>54</v>
       </c>
-      <c r="K122" s="42"/>
+      <c r="K122" s="6"/>
       <c r="L122" s="20">
         <f t="shared" si="6"/>
         <v>54</v>
@@ -8168,11 +9836,11 @@
       </c>
     </row>
     <row r="123" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B123" s="48">
+      <c r="B123" s="42">
         <f t="shared" si="5"/>
         <v>119</v>
       </c>
-      <c r="C123" s="40">
+      <c r="C123" s="37">
         <v>1</v>
       </c>
       <c r="D123" s="7">
@@ -8190,13 +9858,13 @@
       <c r="H123" s="7">
         <v>1</v>
       </c>
-      <c r="I123" s="55">
-        <v>1</v>
-      </c>
-      <c r="J123" s="57">
+      <c r="I123" s="46">
+        <v>1</v>
+      </c>
+      <c r="J123" s="48">
         <v>55</v>
       </c>
-      <c r="K123" s="42"/>
+      <c r="K123" s="6"/>
       <c r="L123" s="20">
         <f t="shared" si="6"/>
         <v>55</v>
@@ -8207,11 +9875,11 @@
       </c>
     </row>
     <row r="124" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B124" s="48">
+      <c r="B124" s="42">
         <f t="shared" si="5"/>
         <v>120</v>
       </c>
-      <c r="C124" s="40">
+      <c r="C124" s="37">
         <v>1</v>
       </c>
       <c r="D124" s="7">
@@ -8229,13 +9897,13 @@
       <c r="H124" s="7">
         <v>0</v>
       </c>
-      <c r="I124" s="55">
-        <v>0</v>
-      </c>
-      <c r="J124" s="57">
+      <c r="I124" s="46">
+        <v>0</v>
+      </c>
+      <c r="J124" s="48">
         <v>56</v>
       </c>
-      <c r="K124" s="42"/>
+      <c r="K124" s="6"/>
       <c r="L124" s="20">
         <f t="shared" si="6"/>
         <v>56</v>
@@ -8246,11 +9914,11 @@
       </c>
     </row>
     <row r="125" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B125" s="48">
+      <c r="B125" s="42">
         <f t="shared" si="5"/>
         <v>121</v>
       </c>
-      <c r="C125" s="40">
+      <c r="C125" s="37">
         <v>1</v>
       </c>
       <c r="D125" s="7">
@@ -8268,13 +9936,13 @@
       <c r="H125" s="7">
         <v>0</v>
       </c>
-      <c r="I125" s="55">
-        <v>1</v>
-      </c>
-      <c r="J125" s="57">
+      <c r="I125" s="46">
+        <v>1</v>
+      </c>
+      <c r="J125" s="48">
         <v>57</v>
       </c>
-      <c r="K125" s="42"/>
+      <c r="K125" s="6"/>
       <c r="L125" s="20">
         <f t="shared" si="6"/>
         <v>57</v>
@@ -8285,11 +9953,11 @@
       </c>
     </row>
     <row r="126" spans="2:13" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B126" s="48">
+      <c r="B126" s="42">
         <f t="shared" si="5"/>
         <v>122</v>
       </c>
-      <c r="C126" s="40">
+      <c r="C126" s="37">
         <v>1</v>
       </c>
       <c r="D126" s="7">
@@ -8307,13 +9975,13 @@
       <c r="H126" s="7">
         <v>1</v>
       </c>
-      <c r="I126" s="55">
-        <v>0</v>
-      </c>
-      <c r="J126" s="57">
+      <c r="I126" s="46">
+        <v>0</v>
+      </c>
+      <c r="J126" s="48">
         <v>58</v>
       </c>
-      <c r="K126" s="42"/>
+      <c r="K126" s="6"/>
       <c r="L126" s="20">
         <f t="shared" si="6"/>
         <v>58</v>
@@ -8324,11 +9992,11 @@
       </c>
     </row>
     <row r="127" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B127" s="48">
+      <c r="B127" s="42">
         <f t="shared" si="5"/>
         <v>123</v>
       </c>
-      <c r="C127" s="40">
+      <c r="C127" s="37">
         <v>1</v>
       </c>
       <c r="D127" s="7">
@@ -8346,13 +10014,13 @@
       <c r="H127" s="7">
         <v>1</v>
       </c>
-      <c r="I127" s="55">
-        <v>1</v>
-      </c>
-      <c r="J127" s="57">
+      <c r="I127" s="46">
+        <v>1</v>
+      </c>
+      <c r="J127" s="48">
         <v>59</v>
       </c>
-      <c r="K127" s="42"/>
+      <c r="K127" s="6"/>
       <c r="L127" s="20">
         <v>123</v>
       </c>
@@ -8362,11 +10030,11 @@
       </c>
     </row>
     <row r="128" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B128" s="48">
+      <c r="B128" s="42">
         <f t="shared" si="5"/>
         <v>124</v>
       </c>
-      <c r="C128" s="40">
+      <c r="C128" s="37">
         <v>1</v>
       </c>
       <c r="D128" s="7">
@@ -8384,13 +10052,13 @@
       <c r="H128" s="7">
         <v>0</v>
       </c>
-      <c r="I128" s="55">
-        <v>0</v>
-      </c>
-      <c r="J128" s="57">
+      <c r="I128" s="46">
+        <v>0</v>
+      </c>
+      <c r="J128" s="48">
         <v>60</v>
       </c>
-      <c r="K128" s="42"/>
+      <c r="K128" s="6"/>
       <c r="L128" s="20">
         <v>124</v>
       </c>
@@ -8400,11 +10068,11 @@
       </c>
     </row>
     <row r="129" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B129" s="48">
+      <c r="B129" s="42">
         <f t="shared" si="5"/>
         <v>125</v>
       </c>
-      <c r="C129" s="40">
+      <c r="C129" s="37">
         <v>1</v>
       </c>
       <c r="D129" s="7">
@@ -8422,13 +10090,13 @@
       <c r="H129" s="7">
         <v>0</v>
       </c>
-      <c r="I129" s="55">
-        <v>1</v>
-      </c>
-      <c r="J129" s="57">
+      <c r="I129" s="46">
+        <v>1</v>
+      </c>
+      <c r="J129" s="48">
         <v>61</v>
       </c>
-      <c r="K129" s="42"/>
+      <c r="K129" s="6"/>
       <c r="L129" s="20">
         <v>125</v>
       </c>
@@ -8438,11 +10106,11 @@
       </c>
     </row>
     <row r="130" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B130" s="48">
+      <c r="B130" s="42">
         <f t="shared" si="5"/>
         <v>126</v>
       </c>
-      <c r="C130" s="40">
+      <c r="C130" s="37">
         <v>1</v>
       </c>
       <c r="D130" s="7">
@@ -8460,13 +10128,13 @@
       <c r="H130" s="7">
         <v>1</v>
       </c>
-      <c r="I130" s="55">
-        <v>0</v>
-      </c>
-      <c r="J130" s="57">
+      <c r="I130" s="46">
+        <v>0</v>
+      </c>
+      <c r="J130" s="48">
         <v>62</v>
       </c>
-      <c r="K130" s="42"/>
+      <c r="K130" s="6"/>
       <c r="L130" s="20">
         <v>126</v>
       </c>
@@ -8476,11 +10144,11 @@
       </c>
     </row>
     <row r="131" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B131" s="49">
+      <c r="B131" s="43">
         <f t="shared" si="5"/>
         <v>127</v>
       </c>
-      <c r="C131" s="38">
+      <c r="C131" s="35">
         <v>1</v>
       </c>
       <c r="D131" s="12">
@@ -8498,13 +10166,13 @@
       <c r="H131" s="12">
         <v>1</v>
       </c>
-      <c r="I131" s="56">
-        <v>1</v>
-      </c>
-      <c r="J131" s="58">
+      <c r="I131" s="47">
+        <v>1</v>
+      </c>
+      <c r="J131" s="49">
         <v>63</v>
       </c>
-      <c r="K131" s="42"/>
+      <c r="K131" s="6"/>
       <c r="L131" s="22">
         <v>127</v>
       </c>
@@ -8524,6 +10192,1437 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A360A7D-484E-4438-B9B8-AF532CC7900D}">
+  <dimension ref="B1:D129"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>7</v>
+      </c>
+      <c r="D9">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>0.11600000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>0.11700000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14">
+        <v>12</v>
+      </c>
+      <c r="D14">
+        <v>0.11700000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15">
+        <v>13</v>
+      </c>
+      <c r="D15">
+        <v>0.11700000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16">
+        <v>14</v>
+      </c>
+      <c r="D16">
+        <v>0.11700000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17">
+        <v>15</v>
+      </c>
+      <c r="D17">
+        <v>0.11799999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18">
+        <v>16</v>
+      </c>
+      <c r="D18">
+        <v>0.11799999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19">
+        <v>17</v>
+      </c>
+      <c r="D19">
+        <v>0.11799999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20">
+        <v>18</v>
+      </c>
+      <c r="D20">
+        <v>0.11799999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21">
+        <v>19</v>
+      </c>
+      <c r="D21">
+        <v>0.11899999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22">
+        <v>20</v>
+      </c>
+      <c r="D22">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23">
+        <v>21</v>
+      </c>
+      <c r="D23">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24">
+        <v>22</v>
+      </c>
+      <c r="D24">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25">
+        <v>23</v>
+      </c>
+      <c r="D25">
+        <v>0.121</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26">
+        <v>24</v>
+      </c>
+      <c r="D26">
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27">
+        <v>25</v>
+      </c>
+      <c r="D27">
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28">
+        <v>26</v>
+      </c>
+      <c r="D28">
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29">
+        <v>27</v>
+      </c>
+      <c r="D29">
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30">
+        <v>28</v>
+      </c>
+      <c r="D30">
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31">
+        <v>29</v>
+      </c>
+      <c r="D31">
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B32" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32">
+        <v>30</v>
+      </c>
+      <c r="D32">
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33">
+        <v>31</v>
+      </c>
+      <c r="D33">
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34">
+        <v>32</v>
+      </c>
+      <c r="D34">
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35">
+        <v>33</v>
+      </c>
+      <c r="D35">
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36">
+        <v>34</v>
+      </c>
+      <c r="D36">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B37" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37">
+        <v>35</v>
+      </c>
+      <c r="D37">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38">
+        <v>36</v>
+      </c>
+      <c r="D38">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39">
+        <v>37</v>
+      </c>
+      <c r="D39">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B40" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40">
+        <v>38</v>
+      </c>
+      <c r="D40">
+        <v>0.127</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41">
+        <v>39</v>
+      </c>
+      <c r="D41">
+        <v>0.127</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42">
+        <v>40</v>
+      </c>
+      <c r="D42">
+        <v>0.127</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B43" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43">
+        <v>41</v>
+      </c>
+      <c r="D43">
+        <v>0.127</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B44" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44">
+        <v>42</v>
+      </c>
+      <c r="D44">
+        <v>0.128</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45">
+        <v>43</v>
+      </c>
+      <c r="D45">
+        <v>0.128</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B46" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46">
+        <v>44</v>
+      </c>
+      <c r="D46">
+        <v>0.129</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47">
+        <v>45</v>
+      </c>
+      <c r="D47">
+        <v>0.129</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B48" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48">
+        <v>46</v>
+      </c>
+      <c r="D48">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49">
+        <v>47</v>
+      </c>
+      <c r="D49">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50">
+        <v>48</v>
+      </c>
+      <c r="D50">
+        <v>0.13100000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B51" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51">
+        <v>49</v>
+      </c>
+      <c r="D51">
+        <v>0.13100000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B52" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52">
+        <v>50</v>
+      </c>
+      <c r="D52">
+        <v>0.13100000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53">
+        <v>51</v>
+      </c>
+      <c r="D53">
+        <v>0.13100000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54">
+        <v>52</v>
+      </c>
+      <c r="D54">
+        <v>0.13200000000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B55" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55">
+        <v>53</v>
+      </c>
+      <c r="D55">
+        <v>0.13200000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56">
+        <v>54</v>
+      </c>
+      <c r="D56">
+        <v>0.13300000000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B57" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57">
+        <v>55</v>
+      </c>
+      <c r="D57">
+        <v>0.13200000000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B58" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58">
+        <v>56</v>
+      </c>
+      <c r="D58">
+        <v>0.13300000000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B59" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59">
+        <v>57</v>
+      </c>
+      <c r="D59">
+        <v>0.13300000000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B60" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60">
+        <v>58</v>
+      </c>
+      <c r="D60">
+        <v>0.13400000000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B61" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61">
+        <v>59</v>
+      </c>
+      <c r="D61">
+        <v>0.13400000000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B62" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62">
+        <v>60</v>
+      </c>
+      <c r="D62">
+        <v>0.13500000000000001</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B63" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63">
+        <v>61</v>
+      </c>
+      <c r="D63">
+        <v>0.13500000000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B64" t="s">
+        <v>17</v>
+      </c>
+      <c r="C64">
+        <v>62</v>
+      </c>
+      <c r="D64">
+        <v>0.13500000000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B65" t="s">
+        <v>17</v>
+      </c>
+      <c r="C65">
+        <v>63</v>
+      </c>
+      <c r="D65">
+        <v>0.13500000000000001</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B66" t="s">
+        <v>17</v>
+      </c>
+      <c r="C66">
+        <v>64</v>
+      </c>
+      <c r="D66">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B67" t="s">
+        <v>17</v>
+      </c>
+      <c r="C67">
+        <v>65</v>
+      </c>
+      <c r="D67">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B68" t="s">
+        <v>17</v>
+      </c>
+      <c r="C68">
+        <v>66</v>
+      </c>
+      <c r="D68">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B69" t="s">
+        <v>17</v>
+      </c>
+      <c r="C69">
+        <v>67</v>
+      </c>
+      <c r="D69">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B70" t="s">
+        <v>17</v>
+      </c>
+      <c r="C70">
+        <v>68</v>
+      </c>
+      <c r="D70">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B71" t="s">
+        <v>17</v>
+      </c>
+      <c r="C71">
+        <v>69</v>
+      </c>
+      <c r="D71">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B72" t="s">
+        <v>17</v>
+      </c>
+      <c r="C72">
+        <v>70</v>
+      </c>
+      <c r="D72">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B73" t="s">
+        <v>17</v>
+      </c>
+      <c r="C73">
+        <v>71</v>
+      </c>
+      <c r="D73">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B74" t="s">
+        <v>17</v>
+      </c>
+      <c r="C74">
+        <v>72</v>
+      </c>
+      <c r="D74">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B75" t="s">
+        <v>17</v>
+      </c>
+      <c r="C75">
+        <v>73</v>
+      </c>
+      <c r="D75">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B76" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76">
+        <v>74</v>
+      </c>
+      <c r="D76">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B77" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77">
+        <v>75</v>
+      </c>
+      <c r="D77">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B78" t="s">
+        <v>17</v>
+      </c>
+      <c r="C78">
+        <v>76</v>
+      </c>
+      <c r="D78">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B79" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79">
+        <v>77</v>
+      </c>
+      <c r="D79">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B80" t="s">
+        <v>17</v>
+      </c>
+      <c r="C80">
+        <v>78</v>
+      </c>
+      <c r="D80">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B81" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81">
+        <v>79</v>
+      </c>
+      <c r="D81">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B82" t="s">
+        <v>17</v>
+      </c>
+      <c r="C82">
+        <v>80</v>
+      </c>
+      <c r="D82">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B83" t="s">
+        <v>17</v>
+      </c>
+      <c r="C83">
+        <v>81</v>
+      </c>
+      <c r="D83">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B84" t="s">
+        <v>17</v>
+      </c>
+      <c r="C84">
+        <v>82</v>
+      </c>
+      <c r="D84">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B85" t="s">
+        <v>17</v>
+      </c>
+      <c r="C85">
+        <v>83</v>
+      </c>
+      <c r="D85">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B86" t="s">
+        <v>17</v>
+      </c>
+      <c r="C86">
+        <v>84</v>
+      </c>
+      <c r="D86">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B87" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87">
+        <v>85</v>
+      </c>
+      <c r="D87">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B88" t="s">
+        <v>17</v>
+      </c>
+      <c r="C88">
+        <v>86</v>
+      </c>
+      <c r="D88">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B89" t="s">
+        <v>17</v>
+      </c>
+      <c r="C89">
+        <v>87</v>
+      </c>
+      <c r="D89">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B90" t="s">
+        <v>17</v>
+      </c>
+      <c r="C90">
+        <v>88</v>
+      </c>
+      <c r="D90">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B91" t="s">
+        <v>17</v>
+      </c>
+      <c r="C91">
+        <v>89</v>
+      </c>
+      <c r="D91">
+        <v>0.10299999999999999</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B92" t="s">
+        <v>17</v>
+      </c>
+      <c r="C92">
+        <v>90</v>
+      </c>
+      <c r="D92">
+        <v>0.10299999999999999</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B93" t="s">
+        <v>17</v>
+      </c>
+      <c r="C93">
+        <v>91</v>
+      </c>
+      <c r="D93">
+        <v>0.10199999999999999</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B94" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94">
+        <v>92</v>
+      </c>
+      <c r="D94">
+        <v>0.10199999999999999</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B95" t="s">
+        <v>17</v>
+      </c>
+      <c r="C95">
+        <v>93</v>
+      </c>
+      <c r="D95">
+        <v>0.10199999999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B96" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96">
+        <v>94</v>
+      </c>
+      <c r="D96">
+        <v>0.10199999999999999</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B97" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97">
+        <v>95</v>
+      </c>
+      <c r="D97">
+        <v>0.10199999999999999</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B98" t="s">
+        <v>17</v>
+      </c>
+      <c r="C98">
+        <v>96</v>
+      </c>
+      <c r="D98">
+        <v>0.10199999999999999</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B99" t="s">
+        <v>17</v>
+      </c>
+      <c r="C99">
+        <v>97</v>
+      </c>
+      <c r="D99">
+        <v>0.10100000000000001</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B100" t="s">
+        <v>17</v>
+      </c>
+      <c r="C100">
+        <v>98</v>
+      </c>
+      <c r="D100">
+        <v>0.10100000000000001</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B101" t="s">
+        <v>17</v>
+      </c>
+      <c r="C101">
+        <v>99</v>
+      </c>
+      <c r="D101">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B102" t="s">
+        <v>17</v>
+      </c>
+      <c r="C102">
+        <v>100</v>
+      </c>
+      <c r="D102">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B103" t="s">
+        <v>17</v>
+      </c>
+      <c r="C103">
+        <v>101</v>
+      </c>
+      <c r="D103">
+        <v>9.9000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B104" t="s">
+        <v>17</v>
+      </c>
+      <c r="C104">
+        <v>102</v>
+      </c>
+      <c r="D104">
+        <v>9.9000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B105" t="s">
+        <v>17</v>
+      </c>
+      <c r="C105">
+        <v>103</v>
+      </c>
+      <c r="D105">
+        <v>9.8000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C106">
+        <v>104</v>
+      </c>
+      <c r="D106">
+        <v>9.8000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B107" t="s">
+        <v>17</v>
+      </c>
+      <c r="C107">
+        <v>105</v>
+      </c>
+      <c r="D107">
+        <v>9.8000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B108" t="s">
+        <v>17</v>
+      </c>
+      <c r="C108">
+        <v>106</v>
+      </c>
+      <c r="D108">
+        <v>9.8000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B109" t="s">
+        <v>17</v>
+      </c>
+      <c r="C109">
+        <v>107</v>
+      </c>
+      <c r="D109">
+        <v>9.7000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B110" t="s">
+        <v>17</v>
+      </c>
+      <c r="C110">
+        <v>108</v>
+      </c>
+      <c r="D110">
+        <v>9.7000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B111" t="s">
+        <v>17</v>
+      </c>
+      <c r="C111">
+        <v>109</v>
+      </c>
+      <c r="D111">
+        <v>9.6000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B112" t="s">
+        <v>17</v>
+      </c>
+      <c r="C112">
+        <v>110</v>
+      </c>
+      <c r="D112">
+        <v>9.6000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B113" t="s">
+        <v>17</v>
+      </c>
+      <c r="C113">
+        <v>111</v>
+      </c>
+      <c r="D113">
+        <v>9.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B114" t="s">
+        <v>17</v>
+      </c>
+      <c r="C114">
+        <v>112</v>
+      </c>
+      <c r="D114">
+        <v>9.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B115" t="s">
+        <v>17</v>
+      </c>
+      <c r="C115">
+        <v>113</v>
+      </c>
+      <c r="D115">
+        <v>9.4E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B116" t="s">
+        <v>17</v>
+      </c>
+      <c r="C116">
+        <v>114</v>
+      </c>
+      <c r="D116">
+        <v>9.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B117" t="s">
+        <v>17</v>
+      </c>
+      <c r="C117">
+        <v>115</v>
+      </c>
+      <c r="D117">
+        <v>9.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B118" t="s">
+        <v>17</v>
+      </c>
+      <c r="C118">
+        <v>116</v>
+      </c>
+      <c r="D118">
+        <v>9.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B119" t="s">
+        <v>17</v>
+      </c>
+      <c r="C119">
+        <v>117</v>
+      </c>
+      <c r="D119">
+        <v>9.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B120" t="s">
+        <v>17</v>
+      </c>
+      <c r="C120">
+        <v>118</v>
+      </c>
+      <c r="D120">
+        <v>9.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B121" t="s">
+        <v>17</v>
+      </c>
+      <c r="C121">
+        <v>119</v>
+      </c>
+      <c r="D121">
+        <v>9.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B122" t="s">
+        <v>17</v>
+      </c>
+      <c r="C122">
+        <v>120</v>
+      </c>
+      <c r="D122">
+        <v>9.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B123" t="s">
+        <v>17</v>
+      </c>
+      <c r="C123">
+        <v>121</v>
+      </c>
+      <c r="D123">
+        <v>9.0999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B124" t="s">
+        <v>17</v>
+      </c>
+      <c r="C124">
+        <v>122</v>
+      </c>
+      <c r="D124">
+        <v>9.0999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B125" t="s">
+        <v>17</v>
+      </c>
+      <c r="C125">
+        <v>123</v>
+      </c>
+      <c r="D125">
+        <v>9.0999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B126" t="s">
+        <v>17</v>
+      </c>
+      <c r="C126">
+        <v>124</v>
+      </c>
+      <c r="D126">
+        <v>9.0999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B127" t="s">
+        <v>17</v>
+      </c>
+      <c r="C127">
+        <v>125</v>
+      </c>
+      <c r="D127">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B128" t="s">
+        <v>17</v>
+      </c>
+      <c r="C128">
+        <v>126</v>
+      </c>
+      <c r="D128">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B129" t="s">
+        <v>17</v>
+      </c>
+      <c r="C129">
+        <v>127</v>
+      </c>
+      <c r="D129">
+        <v>8.8999999999999996E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF95B47F-3B70-4F63-9D3A-6D1458A5D0F5}">
   <dimension ref="B1:J19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.45"/>
@@ -8549,22 +11648,22 @@
       <c r="H1" s="6"/>
     </row>
     <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="37"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="59"/>
       <c r="H2" s="5"/>
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="39" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="31" t="s">
@@ -8588,10 +11687,10 @@
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B4" s="47">
-        <v>0</v>
-      </c>
-      <c r="C4" s="41">
+      <c r="B4" s="41">
+        <v>0</v>
+      </c>
+      <c r="C4" s="38">
         <v>0</v>
       </c>
       <c r="D4" s="4">
@@ -8617,10 +11716,10 @@
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B5" s="48">
-        <v>1</v>
-      </c>
-      <c r="C5" s="40">
+      <c r="B5" s="42">
+        <v>1</v>
+      </c>
+      <c r="C5" s="37">
         <v>0</v>
       </c>
       <c r="D5" s="7">
@@ -8646,10 +11745,10 @@
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B6" s="48">
+      <c r="B6" s="42">
         <v>2</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="37">
         <v>0</v>
       </c>
       <c r="D6" s="7">
@@ -8675,10 +11774,10 @@
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B7" s="48">
+      <c r="B7" s="42">
         <v>3</v>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="37">
         <v>0</v>
       </c>
       <c r="D7" s="7">
@@ -8704,10 +11803,10 @@
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B8" s="48">
+      <c r="B8" s="42">
         <v>4</v>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="37">
         <v>0</v>
       </c>
       <c r="D8" s="7">
@@ -8733,10 +11832,10 @@
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B9" s="48">
+      <c r="B9" s="42">
         <v>5</v>
       </c>
-      <c r="C9" s="40">
+      <c r="C9" s="37">
         <v>0</v>
       </c>
       <c r="D9" s="7">
@@ -8762,10 +11861,10 @@
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B10" s="48">
+      <c r="B10" s="42">
         <v>6</v>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="37">
         <v>0</v>
       </c>
       <c r="D10" s="7">
@@ -8791,10 +11890,10 @@
       </c>
     </row>
     <row r="11" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="49">
+      <c r="B11" s="43">
         <v>7</v>
       </c>
-      <c r="C11" s="38">
+      <c r="C11" s="35">
         <v>0</v>
       </c>
       <c r="D11" s="12">
@@ -8820,7 +11919,7 @@
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B12" s="50">
+      <c r="B12" s="44">
         <v>8</v>
       </c>
       <c r="C12" s="3">
@@ -8849,7 +11948,7 @@
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B13" s="48">
+      <c r="B13" s="42">
         <v>9</v>
       </c>
       <c r="C13" s="9">
@@ -8878,7 +11977,7 @@
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B14" s="48">
+      <c r="B14" s="42">
         <v>10</v>
       </c>
       <c r="C14" s="9">
@@ -8907,7 +12006,7 @@
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B15" s="48">
+      <c r="B15" s="42">
         <v>11</v>
       </c>
       <c r="C15" s="9">
@@ -8936,7 +12035,7 @@
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B16" s="48">
+      <c r="B16" s="42">
         <v>12</v>
       </c>
       <c r="C16" s="9">
@@ -8965,7 +12064,7 @@
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B17" s="48">
+      <c r="B17" s="42">
         <v>13</v>
       </c>
       <c r="C17" s="9">
@@ -8994,7 +12093,7 @@
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B18" s="48">
+      <c r="B18" s="42">
         <v>14</v>
       </c>
       <c r="C18" s="9">
@@ -9023,7 +12122,7 @@
       </c>
     </row>
     <row r="19" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B19" s="49">
+      <c r="B19" s="43">
         <v>15</v>
       </c>
       <c r="C19" s="11">
@@ -9038,7 +12137,7 @@
       <c r="F19" s="12">
         <v>1</v>
       </c>
-      <c r="G19" s="62">
+      <c r="G19" s="53">
         <f t="shared" si="2"/>
         <v>-7</v>
       </c>
